--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_17_37.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_17_37.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3009348.159124365</v>
+        <v>3034275.602362832</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8995212.13897563</v>
+        <v>8995212.138975637</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8995212.13897563</v>
+        <v>8995212.138975637</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48098317.59129457</v>
+        <v>48098317.59129458</v>
       </c>
     </row>
   </sheetData>
@@ -660,19 +660,19 @@
         <v>49.47457824299391</v>
       </c>
       <c r="D2" t="n">
-        <v>10.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>4.363289606868648</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>4.889628708011855</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>2.917171281991102</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>394.1961274758764</v>
+        <v>399.4049501608138</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -681,10 +681,10 @@
         <v>434.7319961948391</v>
       </c>
       <c r="K2" t="n">
-        <v>364.1232814070352</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>316.1561646426481</v>
+        <v>338.4099798994974</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -699,13 +699,13 @@
         <v>350.4651052668121</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>341.869466150186</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>93.00251005209705</v>
       </c>
       <c r="S2" t="n">
-        <v>75.70208740031285</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>182.9976018290664</v>
@@ -736,22 +736,22 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>77.72933682745231</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>327.8264079411381</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -784,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>458.2138584551773</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>3.545774651476108</v>
@@ -796,10 +796,10 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>32.37314290982852</v>
+        <v>319.28150313705</v>
       </c>
       <c r="X3" t="n">
-        <v>419.8627394453875</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -900,7 +900,7 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F5" t="n">
         <v>4.889628708011855</v>
@@ -909,46 +909,46 @@
         <v>2.917171281991102</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>399.4049501608138</v>
       </c>
       <c r="I5" t="n">
-        <v>117.6893104364534</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>4.427259608682391</v>
+        <v>434.7319961948391</v>
       </c>
       <c r="K5" t="n">
-        <v>364.1232814070352</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>98.11745131649535</v>
       </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>471</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>399.6834524886652</v>
       </c>
       <c r="P5" t="n">
-        <v>350.4651052668121</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>275.4609012288048</v>
+        <v>461.6271</v>
       </c>
       <c r="R5" t="n">
         <v>198.1003224463849</v>
       </c>
       <c r="S5" t="n">
-        <v>75.70208740031285</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>182.9976018290664</v>
       </c>
       <c r="U5" t="n">
-        <v>331.9238646681157</v>
+        <v>249.1540804682087</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -957,7 +957,7 @@
         <v>238.3734759809475</v>
       </c>
       <c r="X5" t="n">
-        <v>192.2818334606677</v>
+        <v>64.67477572965832</v>
       </c>
       <c r="Y5" t="n">
         <v>111.3174326828064</v>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>115.6949632036871</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>119.3624388018133</v>
+        <v>454.2726926266453</v>
       </c>
       <c r="S6" t="n">
         <v>58.21385845517733</v>
@@ -1027,16 +1027,16 @@
         <v>3.545774651476108</v>
       </c>
       <c r="U6" t="n">
-        <v>400.1807842884886</v>
+        <v>0.1807842884886099</v>
       </c>
       <c r="V6" t="n">
-        <v>414.5106671915202</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
         <v>432.3731429098285</v>
       </c>
       <c r="X6" t="n">
-        <v>223.6345867128588</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1140,16 +1140,16 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F8" t="n">
-        <v>4.889628708011855</v>
+        <v>399.0857561838882</v>
       </c>
       <c r="G8" t="n">
-        <v>46.79746430236159</v>
+        <v>2.917171281991102</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>117.6893104364534</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>4.427259608682391</v>
@@ -1161,13 +1161,13 @@
         <v>338.4099798994974</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>471</v>
       </c>
       <c r="N8" t="n">
-        <v>408.0509213293074</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>399.6834524886652</v>
+        <v>336.7343738179728</v>
       </c>
       <c r="P8" t="n">
         <v>350.4651052668121</v>
@@ -1191,7 +1191,7 @@
         <v>229.8510241668239</v>
       </c>
       <c r="W8" t="n">
-        <v>471</v>
+        <v>238.3734759809475</v>
       </c>
       <c r="X8" t="n">
         <v>192.2818334606677</v>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
@@ -1225,10 +1225,10 @@
         <v>325.289988705216</v>
       </c>
       <c r="H9" t="n">
-        <v>327.8264079411381</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>201.6485557026693</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1252,16 +1252,16 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>115.6949632036871</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>320.4316468225588</v>
+        <v>119.3624388018133</v>
       </c>
       <c r="S9" t="n">
         <v>58.21385845517733</v>
       </c>
       <c r="T9" t="n">
-        <v>3.545774651476108</v>
+        <v>104.1284404278701</v>
       </c>
       <c r="U9" t="n">
         <v>0.1807842884886099</v>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>259.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -1380,10 +1380,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>180.9171712819911</v>
       </c>
       <c r="H11" t="n">
-        <v>177.4049501608139</v>
+        <v>172.4000940583645</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1416,25 +1416,25 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>253.7020874003128</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>360.9976018290664</v>
       </c>
       <c r="U11" t="n">
-        <v>427.1540804682086</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>407.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>348.5987671860237</v>
+        <v>416.3734759809475</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>289.3174326828064</v>
       </c>
     </row>
     <row r="12">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>162.5565566463266</v>
       </c>
       <c r="C12" t="n">
         <v>139.0999124455193</v>
@@ -1453,13 +1453,13 @@
         <v>125.9376868977026</v>
       </c>
       <c r="E12" t="n">
-        <v>120.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>117.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>103.289988705216</v>
       </c>
       <c r="H12" t="n">
         <v>105.8264079411381</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>236.2138584551773</v>
+        <v>146.0186466832137</v>
       </c>
       <c r="T12" t="n">
         <v>181.5457746514761</v>
@@ -1507,7 +1507,7 @@
         <v>192.5106671915202</v>
       </c>
       <c r="W12" t="n">
-        <v>54.9792363576662</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>197.8627394453875</v>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>65.11380033707866</v>
       </c>
       <c r="C13" t="n">
         <v>50.72524664804467</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>63.53621805555548</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1550,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>22.73356068638896</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>311.5232929208108</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>69.23071556221782</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1589,10 +1589,10 @@
         <v>4.372809838709685</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>25.44364543010755</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>65.46535284946236</v>
       </c>
     </row>
     <row r="14">
@@ -1602,25 +1602,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>211.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>179.4745782429939</v>
       </c>
       <c r="D14" t="n">
-        <v>140.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>134.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>134.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>132.9171712819911</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>129.4049501608138</v>
+        <v>129.4049501608139</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1629,10 +1629,10 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>30.21724844495908</v>
       </c>
       <c r="L14" t="n">
-        <v>30.21724844493528</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1653,22 +1653,22 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>205.7020874003128</v>
       </c>
       <c r="T14" t="n">
-        <v>312.9976018290664</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>379.1540804682086</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>368.3734759809475</v>
       </c>
       <c r="X14" t="n">
-        <v>210.1536787920237</v>
+        <v>190.066905457048</v>
       </c>
       <c r="Y14" t="n">
         <v>241.3174326828064</v>
@@ -1696,10 +1696,10 @@
         <v>69.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>55.28998870521605</v>
+        <v>55.28998870521603</v>
       </c>
       <c r="H15" t="n">
-        <v>57.82640794113809</v>
+        <v>57.82640794113811</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1796,19 +1796,19 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>243.5113539602095</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>62.23513602579997</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>371.8653399512283</v>
       </c>
       <c r="Q16" t="n">
-        <v>237.9558331036276</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>439.6559968336101</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>85.80539773564232</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.984635772535326</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>134.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>132.9171712819911</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>129.4049501608138</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>30.21724844492343</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>30.21724844490169</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1890,13 +1890,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>205.7020874003128</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>312.9976018290664</v>
       </c>
       <c r="U17" t="n">
-        <v>379.1540804682087</v>
+        <v>258.6507771621815</v>
       </c>
       <c r="V17" t="n">
         <v>359.8510241668239</v>
@@ -1933,10 +1933,10 @@
         <v>69.63624233787687</v>
       </c>
       <c r="G18" t="n">
-        <v>55.28998870521605</v>
+        <v>55.28998870521603</v>
       </c>
       <c r="H18" t="n">
-        <v>57.82640794113809</v>
+        <v>57.82640794113811</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2039,13 +2039,13 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>339.1369612472819</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>424.280266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>339.1369612472819</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2103,7 +2103,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>30.21724844493388</v>
+        <v>30.21724844492164</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2127,13 +2127,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>205.7020874003128</v>
       </c>
       <c r="T20" t="n">
         <v>312.9976018290664</v>
       </c>
       <c r="U20" t="n">
-        <v>379.1540804682086</v>
+        <v>379.1540804682087</v>
       </c>
       <c r="V20" t="n">
         <v>359.8510241668239</v>
@@ -2142,10 +2142,10 @@
         <v>368.3734759809475</v>
       </c>
       <c r="X20" t="n">
-        <v>322.2818334606677</v>
+        <v>201.7785301546406</v>
       </c>
       <c r="Y20" t="n">
-        <v>85.19878409428571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2170,10 +2170,10 @@
         <v>69.63624233787687</v>
       </c>
       <c r="G21" t="n">
-        <v>55.28998870521603</v>
+        <v>55.28998870521605</v>
       </c>
       <c r="H21" t="n">
-        <v>57.82640794113811</v>
+        <v>57.82640794113809</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2234,13 +2234,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>17.11380033707866</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>15.53621805555548</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -2264,13 +2264,13 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>11.17819003438444</v>
+        <v>97.51507078072996</v>
       </c>
       <c r="M22" t="n">
         <v>191.5531359927138</v>
       </c>
       <c r="N22" t="n">
-        <v>243.5113539602095</v>
+        <v>107.0591019717673</v>
       </c>
       <c r="O22" t="n">
         <v>317.1745476855723</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>17.46535284946236</v>
       </c>
     </row>
     <row r="23">
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>211.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>179.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>140.3391557398498</v>
@@ -2325,7 +2325,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>134.8896287080119</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>30.21724844495908</v>
+        <v>30.21724844494088</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>312.9976018290664</v>
       </c>
       <c r="U23" t="n">
-        <v>213.7447976887285</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>359.8510241668239</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>368.3734759809475</v>
       </c>
       <c r="X23" t="n">
-        <v>322.2818334606677</v>
+        <v>64.38639349218126</v>
       </c>
       <c r="Y23" t="n">
         <v>241.3174326828064</v>
@@ -2510,16 +2510,16 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>317.1745476855723</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>424.280266425598</v>
+        <v>323.76123083927</v>
       </c>
       <c r="R25" t="n">
-        <v>21.96241356170969</v>
+        <v>439.6559968336101</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2550,25 +2550,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>283.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>251.4745782429939</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>150.3770510659631</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>206.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>204.9171712819911</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>201.4049501608139</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2604,16 +2604,16 @@
         <v>277.7020874003128</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>384.9976018290664</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>451.1540804682086</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>193.4457009050213</v>
       </c>
       <c r="W26" t="n">
-        <v>440.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -2632,19 +2632,19 @@
         <v>186.5565566463266</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>163.0999124455193</v>
       </c>
       <c r="D27" t="n">
-        <v>149.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>144.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>141.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>127.289988705216</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>129.8264079411381</v>
@@ -2680,13 +2680,13 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>235.1412089213397</v>
       </c>
       <c r="T27" t="n">
         <v>205.5457746514761</v>
       </c>
       <c r="U27" t="n">
-        <v>36.88589049263981</v>
+        <v>202.1807842884886</v>
       </c>
       <c r="V27" t="n">
         <v>216.5106671915202</v>
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>38.60060931102614</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -2720,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>76.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -2744,7 +2744,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>120.0231510789265</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -2759,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>157.8053977356423</v>
       </c>
       <c r="T28" t="n">
         <v>10.41423863740525</v>
@@ -2787,10 +2787,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>213.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>181.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>142.3391557398498</v>
@@ -2802,10 +2802,10 @@
         <v>136.8896287080119</v>
       </c>
       <c r="G29" t="n">
-        <v>134.9171712819911</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>131.4049501608138</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2814,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>226.3018055934899</v>
+        <v>226.301805594229</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2844,10 +2844,10 @@
         <v>314.9976018290664</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>381.1540804682087</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>203.0007235648752</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -2856,7 +2856,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>165.6762240745169</v>
+        <v>243.3174326828064</v>
       </c>
     </row>
     <row r="30">
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>116.5565566463266</v>
+        <v>25.86086594080836</v>
       </c>
       <c r="C30" t="n">
         <v>93.09991244551929</v>
@@ -2929,7 +2929,7 @@
         <v>146.5106671915202</v>
       </c>
       <c r="W30" t="n">
-        <v>73.67745220431013</v>
+        <v>164.3731429098285</v>
       </c>
       <c r="X30" t="n">
         <v>151.8627394453875</v>
@@ -2945,19 +2945,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>4.725246648044674</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>17.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>12.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>6.382855967741932</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -2975,13 +2975,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>99.51507078072996</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>193.5531359927138</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>245.5113539602095</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>214.3538331036276</v>
       </c>
       <c r="R31" t="n">
-        <v>37.22589050874474</v>
+        <v>441.6559968336101</v>
       </c>
       <c r="S31" t="n">
         <v>87.80539773564232</v>
@@ -3014,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>19.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>213.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -3033,16 +3033,16 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>136.3632896068686</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>136.8896287080119</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>134.9171712819911</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>131.4049501608138</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3051,10 +3051,10 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>226.3018055942551</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>226.3018055942206</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3078,22 +3078,22 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>314.9976018290664</v>
       </c>
       <c r="U32" t="n">
-        <v>381.1540804682086</v>
+        <v>381.1540804682087</v>
       </c>
       <c r="V32" t="n">
         <v>361.8510241668239</v>
       </c>
       <c r="W32" t="n">
-        <v>370.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>324.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>114.1042729677775</v>
+        <v>168.1862537782153</v>
       </c>
     </row>
     <row r="33">
@@ -3112,16 +3112,16 @@
         <v>79.93768689770263</v>
       </c>
       <c r="E33" t="n">
-        <v>55.61264885427123</v>
+        <v>74.67209722191262</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>71.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>57.28998870521603</v>
+        <v>57.28998870521605</v>
       </c>
       <c r="H33" t="n">
-        <v>59.82640794113811</v>
+        <v>59.82640794113809</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>251.3624388018133</v>
+        <v>160.6667480962949</v>
       </c>
       <c r="S33" t="n">
         <v>190.2138584551773</v>
@@ -3182,19 +3182,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>4.725246648044674</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>17.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>12.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>6.382855967741932</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -3224,16 +3224,16 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>373.8653399512283</v>
       </c>
       <c r="Q34" t="n">
-        <v>134.1494544087881</v>
+        <v>369.9498877216517</v>
       </c>
       <c r="R34" t="n">
-        <v>441.6559968336101</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>87.80539773564232</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3251,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>19.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3264,22 +3264,22 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>17.32464622424187</v>
+        <v>181.4745782429939</v>
       </c>
       <c r="D35" t="n">
-        <v>142.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>136.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>136.8896287080119</v>
       </c>
       <c r="G35" t="n">
-        <v>134.9171712819911</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>131.4049501608138</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>179.4002327109212</v>
+        <v>226.301805594229</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>19.02361060394761</v>
       </c>
       <c r="T35" t="n">
         <v>314.9976018290664</v>
@@ -3321,7 +3321,7 @@
         <v>381.1540804682087</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>361.8510241668239</v>
       </c>
       <c r="W35" t="n">
         <v>370.3734759809475</v>
@@ -3376,7 +3376,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>88.05106607203876</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -3388,10 +3388,10 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>160.6667480962949</v>
+        <v>251.3624388018133</v>
       </c>
       <c r="S36" t="n">
-        <v>190.2138584551773</v>
+        <v>99.51816774965909</v>
       </c>
       <c r="T36" t="n">
         <v>135.5457746514761</v>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>19.11380033707866</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -3464,7 +3464,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>214.3538331036276</v>
+        <v>175.7746799170866</v>
       </c>
       <c r="R37" t="n">
         <v>441.6559968336101</v>
@@ -3488,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>19.46535284946236</v>
       </c>
     </row>
     <row r="38">
@@ -3516,7 +3516,7 @@
         <v>134.9171712819911</v>
       </c>
       <c r="H38" t="n">
-        <v>131.4049501608139</v>
+        <v>131.4049501608138</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3525,10 +3525,10 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>226.3018055922595</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>226.3018055942178</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -3549,19 +3549,19 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>207.7020874003128</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>207.7199168178555</v>
+        <v>370.3913053984903</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>370.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
         <v>324.2818334606677</v>
@@ -3686,19 +3686,19 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>99.51507078072996</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>193.5531359927138</v>
       </c>
       <c r="N40" t="n">
         <v>245.5113539602095</v>
       </c>
       <c r="O40" t="n">
-        <v>319.1745476855723</v>
+        <v>205.2356669392266</v>
       </c>
       <c r="P40" t="n">
-        <v>179.1293260270982</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -3753,7 +3753,7 @@
         <v>284.9171712819911</v>
       </c>
       <c r="H41" t="n">
-        <v>281.4049501608138</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3786,13 +3786,13 @@
         <v>80.10032244638489</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>357.7020874003128</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>301.1547901632958</v>
       </c>
       <c r="U41" t="n">
-        <v>439.1344947199917</v>
+        <v>455.0000000000034</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>393.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3817,7 +3817,7 @@
         <v>266.5565566463266</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>243.0999124455193</v>
       </c>
       <c r="D42" t="n">
         <v>229.9376868977026</v>
@@ -3826,16 +3826,16 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>221.6362423378769</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>209.8264079411381</v>
       </c>
       <c r="I42" t="n">
-        <v>83.64855570266928</v>
+        <v>31.13501667681349</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3859,31 +3859,31 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>-8.964552603728047e-12</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>19.52123517644743</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>285.5457746514761</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
         <v>282.1807842884886</v>
       </c>
       <c r="V42" t="n">
-        <v>296.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>301.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>281.3913927661343</v>
       </c>
     </row>
     <row r="43">
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>74.26240507474753</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3956,7 +3956,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>74.26240507474752</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>140.5694169563444</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -3990,7 +3990,7 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>399.4049501608138</v>
       </c>
       <c r="I44" t="n">
         <v>117.6893104364534</v>
@@ -4020,25 +4020,25 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>198.1003224463849</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>455.0000000000016</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>455.0000000000017</v>
       </c>
       <c r="U44" t="n">
-        <v>455.000000000016</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>283.0746895635002</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>455.0000000000153</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>455.000000000015</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -4051,28 +4051,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>322.9643552285568</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>325.289988705216</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>201.6485557026693</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,13 +4096,13 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>115.6949632036871</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>235.7573494785818</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>455.0000000000172</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -4114,13 +4114,13 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>432.3731429098285</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="46">
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>508.5688394500926</v>
+        <v>491.0936650543513</v>
       </c>
       <c r="C2" t="n">
-        <v>458.594517992523</v>
+        <v>441.1193435967817</v>
       </c>
       <c r="D2" t="n">
-        <v>448.1509263361091</v>
+        <v>441.1193435967817</v>
       </c>
       <c r="E2" t="n">
-        <v>443.7435630968479</v>
+        <v>441.1193435967817</v>
       </c>
       <c r="F2" t="n">
-        <v>438.8045441998662</v>
+        <v>441.1193435967817</v>
       </c>
       <c r="G2" t="n">
-        <v>435.8579065412893</v>
+        <v>441.1193435967817</v>
       </c>
       <c r="H2" t="n">
         <v>37.68</v>
@@ -4324,49 +4324,49 @@
         <v>64.84677152036454</v>
       </c>
       <c r="K2" t="n">
-        <v>163.3354771698239</v>
+        <v>531.1367715203645</v>
       </c>
       <c r="L2" t="n">
-        <v>310.2758159146237</v>
+        <v>655.5985089956196</v>
       </c>
       <c r="M2" t="n">
-        <v>776.5658159146237</v>
+        <v>1121.88850899562</v>
       </c>
       <c r="N2" t="n">
-        <v>1242.855815914624</v>
+        <v>1588.178508995619</v>
       </c>
       <c r="O2" t="n">
-        <v>1305.425156835164</v>
+        <v>1650.74784991616</v>
       </c>
       <c r="P2" t="n">
-        <v>1417.71</v>
+        <v>1763.032693080996</v>
       </c>
       <c r="Q2" t="n">
         <v>1884</v>
       </c>
       <c r="R2" t="n">
-        <v>1884</v>
+        <v>1790.058070654447</v>
       </c>
       <c r="S2" t="n">
-        <v>1807.533245050189</v>
+        <v>1790.058070654447</v>
       </c>
       <c r="T2" t="n">
-        <v>1622.687182596587</v>
+        <v>1605.212008200845</v>
       </c>
       <c r="U2" t="n">
-        <v>1371.016394244861</v>
+        <v>1353.541219849119</v>
       </c>
       <c r="V2" t="n">
-        <v>1138.8436425612</v>
+        <v>1121.368468165458</v>
       </c>
       <c r="W2" t="n">
-        <v>898.0623536915559</v>
+        <v>880.5871792958144</v>
       </c>
       <c r="X2" t="n">
-        <v>703.8382794888612</v>
+        <v>686.3631050931198</v>
       </c>
       <c r="Y2" t="n">
-        <v>591.3964282941073</v>
+        <v>573.9212538983659</v>
       </c>
     </row>
     <row r="3">
@@ -4376,22 +4376,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>541.8919525839611</v>
+        <v>1118.96821342028</v>
       </c>
       <c r="C3" t="n">
-        <v>177.1445662753558</v>
+        <v>1118.96821342028</v>
       </c>
       <c r="D3" t="n">
-        <v>177.1445662753558</v>
+        <v>1118.96821342028</v>
       </c>
       <c r="E3" t="n">
-        <v>177.1445662753558</v>
+        <v>772.8347818829948</v>
       </c>
       <c r="F3" t="n">
-        <v>177.1445662753558</v>
+        <v>429.7678704305939</v>
       </c>
       <c r="G3" t="n">
-        <v>98.63008463146454</v>
+        <v>429.7678704305939</v>
       </c>
       <c r="H3" t="n">
         <v>98.63008463146454</v>
@@ -4427,25 +4427,25 @@
         <v>1884</v>
       </c>
       <c r="S3" t="n">
-        <v>1421.157718732144</v>
+        <v>1884</v>
       </c>
       <c r="T3" t="n">
-        <v>1417.576128175097</v>
+        <v>1880.418409442953</v>
       </c>
       <c r="U3" t="n">
-        <v>1013.353113742281</v>
+        <v>1476.195395010137</v>
       </c>
       <c r="V3" t="n">
-        <v>998.6958741548865</v>
+        <v>1461.538155422742</v>
       </c>
       <c r="W3" t="n">
-        <v>965.9957298015244</v>
+        <v>1139.031586597439</v>
       </c>
       <c r="X3" t="n">
-        <v>541.8919525839611</v>
+        <v>1118.96821342028</v>
       </c>
       <c r="Y3" t="n">
-        <v>541.8919525839611</v>
+        <v>1118.96821342028</v>
       </c>
     </row>
     <row r="4">
@@ -4534,49 +4534,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>224.861661019495</v>
+        <v>513.8302765055851</v>
       </c>
       <c r="C5" t="n">
-        <v>174.8873395619254</v>
+        <v>463.8559550480154</v>
       </c>
       <c r="D5" t="n">
-        <v>164.4437479055115</v>
+        <v>453.4123633916015</v>
       </c>
       <c r="E5" t="n">
-        <v>164.4437479055115</v>
+        <v>449.0050001523402</v>
       </c>
       <c r="F5" t="n">
-        <v>159.5047290085298</v>
+        <v>444.0659812553586</v>
       </c>
       <c r="G5" t="n">
-        <v>156.558091349953</v>
+        <v>441.1193435967817</v>
       </c>
       <c r="H5" t="n">
-        <v>156.558091349953</v>
+        <v>37.68</v>
       </c>
       <c r="I5" t="n">
         <v>37.68</v>
       </c>
       <c r="J5" t="n">
-        <v>499.4980205972905</v>
+        <v>64.84677152036454</v>
       </c>
       <c r="K5" t="n">
-        <v>597.9867262467499</v>
+        <v>531.1367715203645</v>
       </c>
       <c r="L5" t="n">
-        <v>1064.27672624675</v>
+        <v>898.3182348370358</v>
       </c>
       <c r="M5" t="n">
-        <v>1054.809150489174</v>
+        <v>1364.608234837036</v>
       </c>
       <c r="N5" t="n">
-        <v>1521.099150489174</v>
+        <v>1355.14065907946</v>
       </c>
       <c r="O5" t="n">
-        <v>1583.668491409714</v>
+        <v>1417.71</v>
       </c>
       <c r="P5" t="n">
-        <v>1695.95333457455</v>
+        <v>1884</v>
       </c>
       <c r="Q5" t="n">
         <v>1884</v>
@@ -4585,25 +4585,25 @@
         <v>1683.898664195571</v>
       </c>
       <c r="S5" t="n">
-        <v>1607.43190924576</v>
+        <v>1683.898664195571</v>
       </c>
       <c r="T5" t="n">
-        <v>1422.585846792157</v>
+        <v>1499.052601741968</v>
       </c>
       <c r="U5" t="n">
-        <v>1087.309215814263</v>
+        <v>1247.381813390242</v>
       </c>
       <c r="V5" t="n">
-        <v>855.1364641306022</v>
+        <v>1015.209061706582</v>
       </c>
       <c r="W5" t="n">
-        <v>614.3551752609583</v>
+        <v>774.4277728369377</v>
       </c>
       <c r="X5" t="n">
-        <v>420.1311010582637</v>
+        <v>709.0997165443536</v>
       </c>
       <c r="Y5" t="n">
-        <v>307.6892498635097</v>
+        <v>596.6578653495997</v>
       </c>
     </row>
     <row r="6">
@@ -4658,31 +4658,31 @@
         <v>1823.049915368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1706.186316172892</v>
+        <v>1823.049915368536</v>
       </c>
       <c r="R6" t="n">
-        <v>1585.61819617106</v>
+        <v>1364.188609685056</v>
       </c>
       <c r="S6" t="n">
-        <v>1526.816318943609</v>
+        <v>1305.386732457604</v>
       </c>
       <c r="T6" t="n">
-        <v>1523.234728386562</v>
+        <v>1301.805141900557</v>
       </c>
       <c r="U6" t="n">
-        <v>1119.011713953745</v>
+        <v>1301.622531508144</v>
       </c>
       <c r="V6" t="n">
-        <v>700.3140703259469</v>
+        <v>1286.96529192075</v>
       </c>
       <c r="W6" t="n">
-        <v>263.5735219321807</v>
+        <v>850.2247435269841</v>
       </c>
       <c r="X6" t="n">
-        <v>37.68</v>
+        <v>426.1209663094209</v>
       </c>
       <c r="Y6" t="n">
-        <v>37.68</v>
+        <v>426.1209663094209</v>
       </c>
     </row>
     <row r="7">
@@ -4771,25 +4771,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>273.5925525621608</v>
+        <v>508.5688394500926</v>
       </c>
       <c r="C8" t="n">
-        <v>223.6182311045912</v>
+        <v>458.594517992523</v>
       </c>
       <c r="D8" t="n">
-        <v>213.1746394481773</v>
+        <v>448.1509263361091</v>
       </c>
       <c r="E8" t="n">
-        <v>208.7672762089161</v>
+        <v>443.7435630968479</v>
       </c>
       <c r="F8" t="n">
-        <v>203.8282573119344</v>
+        <v>40.62663765857687</v>
       </c>
       <c r="G8" t="n">
-        <v>156.558091349953</v>
+        <v>37.68</v>
       </c>
       <c r="H8" t="n">
-        <v>156.558091349953</v>
+        <v>37.68</v>
       </c>
       <c r="I8" t="n">
         <v>37.68</v>
@@ -4804,10 +4804,10 @@
         <v>722.4484637220049</v>
       </c>
       <c r="M8" t="n">
-        <v>1188.738463722005</v>
+        <v>712.9808879644291</v>
       </c>
       <c r="N8" t="n">
-        <v>1242.855815914624</v>
+        <v>1179.270887964429</v>
       </c>
       <c r="O8" t="n">
         <v>1305.425156835164</v>
@@ -4834,13 +4834,13 @@
         <v>1138.8436425612</v>
       </c>
       <c r="W8" t="n">
-        <v>663.0860668036241</v>
+        <v>898.0623536915559</v>
       </c>
       <c r="X8" t="n">
-        <v>468.8619926009295</v>
+        <v>703.8382794888612</v>
       </c>
       <c r="Y8" t="n">
-        <v>356.4201414061755</v>
+        <v>591.3964282941073</v>
       </c>
     </row>
     <row r="9">
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1252.531150754269</v>
+        <v>1082.455341463069</v>
       </c>
       <c r="C9" t="n">
-        <v>1252.531150754269</v>
+        <v>717.7079551544634</v>
       </c>
       <c r="D9" t="n">
-        <v>901.0789417666904</v>
+        <v>366.2557461668849</v>
       </c>
       <c r="E9" t="n">
-        <v>901.0789417666904</v>
+        <v>366.2557461668849</v>
       </c>
       <c r="F9" t="n">
-        <v>901.0789417666904</v>
+        <v>366.2557461668849</v>
       </c>
       <c r="G9" t="n">
-        <v>572.5031955998055</v>
+        <v>37.68</v>
       </c>
       <c r="H9" t="n">
-        <v>241.3654098006761</v>
+        <v>37.68</v>
       </c>
       <c r="I9" t="n">
         <v>37.68</v>
@@ -4895,31 +4895,31 @@
         <v>1823.049915368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1706.186316172892</v>
+        <v>1823.049915368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1382.517986049095</v>
+        <v>1702.481795366704</v>
       </c>
       <c r="S9" t="n">
-        <v>1323.716108821644</v>
+        <v>1643.679918139252</v>
       </c>
       <c r="T9" t="n">
-        <v>1320.134518264597</v>
+        <v>1538.499675282818</v>
       </c>
       <c r="U9" t="n">
-        <v>1319.951907872184</v>
+        <v>1538.317064890405</v>
       </c>
       <c r="V9" t="n">
-        <v>1305.29466828479</v>
+        <v>1523.659825303011</v>
       </c>
       <c r="W9" t="n">
-        <v>1272.594523931428</v>
+        <v>1490.959680949649</v>
       </c>
       <c r="X9" t="n">
-        <v>1252.531150754269</v>
+        <v>1470.89630777249</v>
       </c>
       <c r="Y9" t="n">
-        <v>1252.531150754269</v>
+        <v>1470.89630777249</v>
       </c>
     </row>
     <row r="10">
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>216.8769193543575</v>
+        <v>394.5661266064198</v>
       </c>
       <c r="C11" t="n">
-        <v>216.8769193543575</v>
+        <v>394.5661266064198</v>
       </c>
       <c r="D11" t="n">
-        <v>216.8769193543575</v>
+        <v>394.5661266064198</v>
       </c>
       <c r="E11" t="n">
-        <v>216.8769193543575</v>
+        <v>394.5661266064198</v>
       </c>
       <c r="F11" t="n">
-        <v>216.8769193543575</v>
+        <v>394.5661266064198</v>
       </c>
       <c r="G11" t="n">
-        <v>216.8769193543575</v>
+        <v>211.8215091498631</v>
       </c>
       <c r="H11" t="n">
         <v>37.68</v>
@@ -5035,22 +5035,22 @@
         <v>499.5870129874045</v>
       </c>
       <c r="K11" t="n">
-        <v>965.8770129874043</v>
+        <v>605.3949643944396</v>
       </c>
       <c r="L11" t="n">
-        <v>1432.167012987404</v>
+        <v>736.6590842939371</v>
       </c>
       <c r="M11" t="n">
-        <v>1432.167012987404</v>
+        <v>1202.949084293937</v>
       </c>
       <c r="N11" t="n">
-        <v>1694.067072177923</v>
+        <v>1669.239084293937</v>
       </c>
       <c r="O11" t="n">
-        <v>1764.670454214144</v>
+        <v>1739.842466330158</v>
       </c>
       <c r="P11" t="n">
-        <v>1884</v>
+        <v>1859.172012116014</v>
       </c>
       <c r="Q11" t="n">
         <v>1884</v>
@@ -5059,25 +5059,25 @@
         <v>1884</v>
       </c>
       <c r="S11" t="n">
-        <v>1627.735265252209</v>
+        <v>1884</v>
       </c>
       <c r="T11" t="n">
-        <v>1263.091223000627</v>
+        <v>1519.355957748418</v>
       </c>
       <c r="U11" t="n">
-        <v>831.6224548509213</v>
+        <v>1519.355957748418</v>
       </c>
       <c r="V11" t="n">
-        <v>831.6224548509213</v>
+        <v>1107.385226266777</v>
       </c>
       <c r="W11" t="n">
-        <v>479.5024879963519</v>
+        <v>686.8059575991535</v>
       </c>
       <c r="X11" t="n">
-        <v>479.5024879963519</v>
+        <v>686.8059575991535</v>
       </c>
       <c r="Y11" t="n">
-        <v>479.5024879963519</v>
+        <v>394.5661266064198</v>
       </c>
     </row>
     <row r="12">
@@ -5087,19 +5087,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>653.0056028728784</v>
+        <v>635.4479175024777</v>
       </c>
       <c r="C12" t="n">
-        <v>512.5006408066972</v>
+        <v>494.9429554362966</v>
       </c>
       <c r="D12" t="n">
-        <v>385.290856061543</v>
+        <v>367.7331706911424</v>
       </c>
       <c r="E12" t="n">
-        <v>263.3998487666818</v>
+        <v>367.7331706911424</v>
       </c>
       <c r="F12" t="n">
-        <v>144.5753615567052</v>
+        <v>248.9086834811658</v>
       </c>
       <c r="G12" t="n">
         <v>144.5753615567052</v>
@@ -5108,28 +5108,28 @@
         <v>37.68</v>
       </c>
       <c r="I12" t="n">
-        <v>57.82792985435741</v>
+        <v>37.68</v>
       </c>
       <c r="J12" t="n">
-        <v>223.8320755956941</v>
+        <v>203.6841457413367</v>
       </c>
       <c r="K12" t="n">
-        <v>484.8909810297001</v>
+        <v>464.7430511753428</v>
       </c>
       <c r="L12" t="n">
-        <v>852.8742685682964</v>
+        <v>832.7263387139392</v>
       </c>
       <c r="M12" t="n">
-        <v>1051.720760311156</v>
+        <v>1031.572830456798</v>
       </c>
       <c r="N12" t="n">
-        <v>1300.751574069667</v>
+        <v>1341.553728846774</v>
       </c>
       <c r="O12" t="n">
-        <v>1645.683146225084</v>
+        <v>1686.485301002191</v>
       </c>
       <c r="P12" t="n">
-        <v>1843.197845222893</v>
+        <v>1884</v>
       </c>
       <c r="Q12" t="n">
         <v>1884</v>
@@ -5138,25 +5138,25 @@
         <v>1884</v>
       </c>
       <c r="S12" t="n">
-        <v>1645.400142974568</v>
+        <v>1736.506417491703</v>
       </c>
       <c r="T12" t="n">
-        <v>1462.020572619542</v>
+        <v>1553.126847136677</v>
       </c>
       <c r="U12" t="n">
-        <v>1282.039982429149</v>
+        <v>1373.146256946284</v>
       </c>
       <c r="V12" t="n">
-        <v>1087.584763043775</v>
+        <v>1178.69103756091</v>
       </c>
       <c r="W12" t="n">
-        <v>1032.050180864315</v>
+        <v>1178.69103756091</v>
       </c>
       <c r="X12" t="n">
-        <v>832.1888278891757</v>
+        <v>978.8296845857716</v>
       </c>
       <c r="Y12" t="n">
-        <v>653.0056028728784</v>
+        <v>799.6464595694742</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>139.6658614414198</v>
+        <v>156.5504427739418</v>
       </c>
       <c r="C13" t="n">
-        <v>88.42823856460699</v>
+        <v>105.312819897129</v>
       </c>
       <c r="D13" t="n">
-        <v>88.42823856460699</v>
+        <v>41.13482186121437</v>
       </c>
       <c r="E13" t="n">
-        <v>88.42823856460699</v>
+        <v>41.13482186121437</v>
       </c>
       <c r="F13" t="n">
-        <v>88.42823856460699</v>
+        <v>41.13482186121437</v>
       </c>
       <c r="G13" t="n">
-        <v>88.42823856460699</v>
+        <v>41.13482186121437</v>
       </c>
       <c r="H13" t="n">
-        <v>84.97341670339262</v>
+        <v>37.68</v>
       </c>
       <c r="I13" t="n">
-        <v>141.1069231804591</v>
+        <v>93.81350647706651</v>
       </c>
       <c r="J13" t="n">
-        <v>352.3499928493038</v>
+        <v>305.0565761459112</v>
       </c>
       <c r="K13" t="n">
-        <v>352.3499928493038</v>
+        <v>282.0933835333971</v>
       </c>
       <c r="L13" t="n">
-        <v>352.3499928493038</v>
+        <v>282.0933835333971</v>
       </c>
       <c r="M13" t="n">
-        <v>352.3499928493038</v>
+        <v>282.0933835333971</v>
       </c>
       <c r="N13" t="n">
-        <v>352.3499928493038</v>
+        <v>282.0933835333971</v>
       </c>
       <c r="O13" t="n">
-        <v>352.3499928493038</v>
+        <v>282.0933835333971</v>
       </c>
       <c r="P13" t="n">
-        <v>37.68</v>
+        <v>282.0933835333971</v>
       </c>
       <c r="Q13" t="n">
-        <v>37.68</v>
+        <v>282.0933835333971</v>
       </c>
       <c r="R13" t="n">
-        <v>37.68</v>
+        <v>282.0933835333971</v>
       </c>
       <c r="S13" t="n">
-        <v>37.68</v>
+        <v>212.1633678139852</v>
       </c>
       <c r="T13" t="n">
-        <v>51.1299037489688</v>
+        <v>225.613271562954</v>
       </c>
       <c r="U13" t="n">
-        <v>121.4814481905341</v>
+        <v>295.9648160045193</v>
       </c>
       <c r="V13" t="n">
-        <v>144.0828410764801</v>
+        <v>318.5662088904653</v>
       </c>
       <c r="W13" t="n">
-        <v>139.6658614414198</v>
+        <v>314.149229255405</v>
       </c>
       <c r="X13" t="n">
-        <v>139.6658614414198</v>
+        <v>288.4485773058015</v>
       </c>
       <c r="Y13" t="n">
-        <v>139.6658614414198</v>
+        <v>222.3219582659405</v>
       </c>
     </row>
     <row r="14">
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>897.6686603439688</v>
+        <v>485.4000181926025</v>
       </c>
       <c r="C14" t="n">
-        <v>716.3812075732678</v>
+        <v>304.1125654219015</v>
       </c>
       <c r="D14" t="n">
-        <v>574.6244846037226</v>
+        <v>304.1125654219015</v>
       </c>
       <c r="E14" t="n">
-        <v>438.9039900513301</v>
+        <v>168.392070869509</v>
       </c>
       <c r="F14" t="n">
-        <v>302.6518398412171</v>
+        <v>168.392070869509</v>
       </c>
       <c r="G14" t="n">
-        <v>168.3920708695089</v>
+        <v>168.392070869509</v>
       </c>
       <c r="H14" t="n">
         <v>37.68</v>
@@ -5272,22 +5272,22 @@
         <v>499.5870129874045</v>
       </c>
       <c r="K14" t="n">
-        <v>605.3949643944396</v>
+        <v>935.354539810678</v>
       </c>
       <c r="L14" t="n">
-        <v>736.0516870777208</v>
+        <v>1066.618659710176</v>
       </c>
       <c r="M14" t="n">
-        <v>1202.341687077721</v>
+        <v>1532.908659710175</v>
       </c>
       <c r="N14" t="n">
-        <v>1668.631687077721</v>
+        <v>1694.067072177923</v>
       </c>
       <c r="O14" t="n">
-        <v>1739.235069113942</v>
+        <v>1764.670454214144</v>
       </c>
       <c r="P14" t="n">
-        <v>1858.564614899798</v>
+        <v>1884</v>
       </c>
       <c r="Q14" t="n">
         <v>1884</v>
@@ -5296,25 +5296,25 @@
         <v>1884</v>
       </c>
       <c r="S14" t="n">
-        <v>1884</v>
+        <v>1676.220113737058</v>
       </c>
       <c r="T14" t="n">
-        <v>1567.840806233266</v>
+        <v>1676.220113737058</v>
       </c>
       <c r="U14" t="n">
-        <v>1567.840806233266</v>
+        <v>1293.236194072201</v>
       </c>
       <c r="V14" t="n">
-        <v>1567.840806233266</v>
+        <v>1293.236194072201</v>
       </c>
       <c r="W14" t="n">
-        <v>1567.840806233266</v>
+        <v>921.1417738894252</v>
       </c>
       <c r="X14" t="n">
-        <v>1355.564363009</v>
+        <v>729.1550007004878</v>
       </c>
       <c r="Y14" t="n">
-        <v>1111.809380501115</v>
+        <v>485.4000181926025</v>
       </c>
     </row>
     <row r="15">
@@ -5339,25 +5339,25 @@
         <v>151.9389865114688</v>
       </c>
       <c r="G15" t="n">
-        <v>96.09051307185666</v>
+        <v>96.09051307185669</v>
       </c>
       <c r="H15" t="n">
         <v>37.68</v>
       </c>
       <c r="I15" t="n">
-        <v>97.21886312188664</v>
+        <v>37.68</v>
       </c>
       <c r="J15" t="n">
-        <v>263.2230088632234</v>
+        <v>203.6841457413367</v>
       </c>
       <c r="K15" t="n">
-        <v>524.2819142972294</v>
+        <v>464.7430511753428</v>
       </c>
       <c r="L15" t="n">
-        <v>892.2652018358258</v>
+        <v>832.7263387139392</v>
       </c>
       <c r="M15" t="n">
-        <v>1091.111693578685</v>
+        <v>1031.572830456798</v>
       </c>
       <c r="N15" t="n">
         <v>1340.142507337197</v>
@@ -5418,7 +5418,7 @@
         <v>352.164550360351</v>
       </c>
       <c r="G16" t="n">
-        <v>377.2442326406788</v>
+        <v>377.2442326406789</v>
       </c>
       <c r="H16" t="n">
         <v>421.3781617345027</v>
@@ -5439,16 +5439,16 @@
         <v>808.8085128008889</v>
       </c>
       <c r="N16" t="n">
-        <v>808.8085128008889</v>
+        <v>562.8374481946167</v>
       </c>
       <c r="O16" t="n">
-        <v>808.8085128008889</v>
+        <v>499.9736744311824</v>
       </c>
       <c r="P16" t="n">
-        <v>808.8085128008889</v>
+        <v>124.3521189248912</v>
       </c>
       <c r="Q16" t="n">
-        <v>568.4490854234873</v>
+        <v>124.3521189248912</v>
       </c>
       <c r="R16" t="n">
         <v>124.3521189248912</v>
@@ -5482,22 +5482,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>439.8985716397496</v>
+        <v>37.68</v>
       </c>
       <c r="C17" t="n">
-        <v>439.8985716397496</v>
+        <v>37.68</v>
       </c>
       <c r="D17" t="n">
-        <v>439.8985716397496</v>
+        <v>37.68</v>
       </c>
       <c r="E17" t="n">
-        <v>438.9039900513301</v>
+        <v>37.68</v>
       </c>
       <c r="F17" t="n">
-        <v>302.6518398412171</v>
+        <v>37.68</v>
       </c>
       <c r="G17" t="n">
-        <v>168.3920708695089</v>
+        <v>37.68</v>
       </c>
       <c r="H17" t="n">
         <v>37.68</v>
@@ -5506,16 +5506,16 @@
         <v>37.68</v>
       </c>
       <c r="J17" t="n">
-        <v>72.97792655089319</v>
+        <v>499.5870129874045</v>
       </c>
       <c r="K17" t="n">
-        <v>539.2679265508932</v>
+        <v>605.3949643944396</v>
       </c>
       <c r="L17" t="n">
-        <v>670.5320464503907</v>
+        <v>736.0516870777215</v>
       </c>
       <c r="M17" t="n">
-        <v>761.4870721779216</v>
+        <v>1202.341687077721</v>
       </c>
       <c r="N17" t="n">
         <v>1227.777072177923</v>
@@ -5533,25 +5533,25 @@
         <v>1884</v>
       </c>
       <c r="S17" t="n">
-        <v>1884</v>
+        <v>1676.220113737058</v>
       </c>
       <c r="T17" t="n">
-        <v>1884</v>
+        <v>1360.060919970324</v>
       </c>
       <c r="U17" t="n">
-        <v>1501.016080335143</v>
+        <v>1098.797508695393</v>
       </c>
       <c r="V17" t="n">
-        <v>1137.530197338351</v>
+        <v>735.3116256986013</v>
       </c>
       <c r="W17" t="n">
-        <v>765.4357771555756</v>
+        <v>363.217205515826</v>
       </c>
       <c r="X17" t="n">
-        <v>439.8985716397496</v>
+        <v>37.68</v>
       </c>
       <c r="Y17" t="n">
-        <v>439.8985716397496</v>
+        <v>37.68</v>
       </c>
     </row>
     <row r="18">
@@ -5576,34 +5576,34 @@
         <v>151.9389865114688</v>
       </c>
       <c r="G18" t="n">
-        <v>96.09051307185666</v>
+        <v>96.09051307185669</v>
       </c>
       <c r="H18" t="n">
         <v>37.68</v>
       </c>
       <c r="I18" t="n">
-        <v>37.68</v>
+        <v>97.21886312188664</v>
       </c>
       <c r="J18" t="n">
-        <v>203.6841457413367</v>
+        <v>263.2230088632234</v>
       </c>
       <c r="K18" t="n">
-        <v>464.7430511753428</v>
+        <v>524.2819142972294</v>
       </c>
       <c r="L18" t="n">
-        <v>832.7263387139392</v>
+        <v>892.2652018358258</v>
       </c>
       <c r="M18" t="n">
-        <v>1031.572830456798</v>
+        <v>1091.111693578685</v>
       </c>
       <c r="N18" t="n">
-        <v>1280.60364421531</v>
+        <v>1340.142507337197</v>
       </c>
       <c r="O18" t="n">
-        <v>1625.535216370727</v>
+        <v>1685.074079492614</v>
       </c>
       <c r="P18" t="n">
-        <v>1823.049915368536</v>
+        <v>1882.588778490422</v>
       </c>
       <c r="Q18" t="n">
         <v>1882.588778490422</v>
@@ -5655,7 +5655,7 @@
         <v>352.164550360351</v>
       </c>
       <c r="G19" t="n">
-        <v>377.2442326406788</v>
+        <v>377.2442326406789</v>
       </c>
       <c r="H19" t="n">
         <v>421.3781617345027</v>
@@ -5682,10 +5682,10 @@
         <v>808.8085128008889</v>
       </c>
       <c r="P19" t="n">
-        <v>466.2459256824223</v>
+        <v>808.8085128008889</v>
       </c>
       <c r="Q19" t="n">
-        <v>37.68</v>
+        <v>380.2425871184666</v>
       </c>
       <c r="R19" t="n">
         <v>37.68</v>
@@ -5743,25 +5743,25 @@
         <v>37.68</v>
       </c>
       <c r="J20" t="n">
-        <v>73.58532376710933</v>
+        <v>499.5870129874045</v>
       </c>
       <c r="K20" t="n">
-        <v>509.3528505904084</v>
+        <v>630.2229522784252</v>
       </c>
       <c r="L20" t="n">
-        <v>640.616970489906</v>
+        <v>761.4870721779228</v>
       </c>
       <c r="M20" t="n">
-        <v>1106.906970489908</v>
+        <v>761.4870721779228</v>
       </c>
       <c r="N20" t="n">
-        <v>1573.196970489909</v>
+        <v>1227.777072177923</v>
       </c>
       <c r="O20" t="n">
-        <v>1643.800352526131</v>
+        <v>1298.380454214144</v>
       </c>
       <c r="P20" t="n">
-        <v>1763.129898311987</v>
+        <v>1417.71</v>
       </c>
       <c r="Q20" t="n">
         <v>1884</v>
@@ -5770,22 +5770,22 @@
         <v>1884</v>
       </c>
       <c r="S20" t="n">
-        <v>1884</v>
+        <v>1676.220113737058</v>
       </c>
       <c r="T20" t="n">
-        <v>1567.840806233266</v>
+        <v>1360.060919970324</v>
       </c>
       <c r="U20" t="n">
-        <v>1184.856886568409</v>
+        <v>977.0770003054668</v>
       </c>
       <c r="V20" t="n">
-        <v>821.3710035716172</v>
+        <v>613.5911173086749</v>
       </c>
       <c r="W20" t="n">
-        <v>449.2765833888419</v>
+        <v>241.4966971258996</v>
       </c>
       <c r="X20" t="n">
-        <v>123.7393778730159</v>
+        <v>37.68</v>
       </c>
       <c r="Y20" t="n">
         <v>37.68</v>
@@ -5813,7 +5813,7 @@
         <v>151.9389865114688</v>
       </c>
       <c r="G21" t="n">
-        <v>96.09051307185669</v>
+        <v>96.09051307185666</v>
       </c>
       <c r="H21" t="n">
         <v>37.68</v>
@@ -5877,40 +5877,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>352.164550360351</v>
+        <v>317.2361127981883</v>
       </c>
       <c r="C22" t="n">
-        <v>352.164550360351</v>
+        <v>317.2361127981883</v>
       </c>
       <c r="D22" t="n">
-        <v>352.164550360351</v>
+        <v>301.5429632471221</v>
       </c>
       <c r="E22" t="n">
-        <v>352.164550360351</v>
+        <v>301.5429632471221</v>
       </c>
       <c r="F22" t="n">
-        <v>352.164550360351</v>
+        <v>301.5429632471221</v>
       </c>
       <c r="G22" t="n">
-        <v>377.2442326406789</v>
+        <v>326.62264552745</v>
       </c>
       <c r="H22" t="n">
-        <v>421.3781617345027</v>
+        <v>370.7565746212738</v>
       </c>
       <c r="I22" t="n">
-        <v>525.0316682115692</v>
+        <v>474.4100810983403</v>
       </c>
       <c r="J22" t="n">
-        <v>783.794737880414</v>
+        <v>733.173150767185</v>
       </c>
       <c r="K22" t="n">
-        <v>808.8085128008889</v>
+        <v>758.1869256876599</v>
       </c>
       <c r="L22" t="n">
-        <v>797.5174117560562</v>
+        <v>659.6868541919731</v>
       </c>
       <c r="M22" t="n">
-        <v>604.0293956017998</v>
+        <v>466.1988380377168</v>
       </c>
       <c r="N22" t="n">
         <v>358.0583309955276</v>
@@ -5946,7 +5946,7 @@
         <v>352.164550360351</v>
       </c>
       <c r="Y22" t="n">
-        <v>352.164550360351</v>
+        <v>334.5227798053385</v>
       </c>
     </row>
     <row r="23">
@@ -5956,16 +5956,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>360.7241757402462</v>
+        <v>315.6888731796582</v>
       </c>
       <c r="C23" t="n">
-        <v>179.4367229695453</v>
+        <v>315.6888731796582</v>
       </c>
       <c r="D23" t="n">
-        <v>37.68</v>
+        <v>173.932150210113</v>
       </c>
       <c r="E23" t="n">
-        <v>37.68</v>
+        <v>173.932150210113</v>
       </c>
       <c r="F23" t="n">
         <v>37.68</v>
@@ -5983,22 +5983,22 @@
         <v>73.58532376710933</v>
       </c>
       <c r="K23" t="n">
-        <v>509.352850590383</v>
+        <v>178.785877957928</v>
       </c>
       <c r="L23" t="n">
-        <v>640.6169704898805</v>
+        <v>645.075877957928</v>
       </c>
       <c r="M23" t="n">
-        <v>1106.906970489883</v>
+        <v>761.4870721779228</v>
       </c>
       <c r="N23" t="n">
-        <v>1227.77707217792</v>
+        <v>1227.777072177923</v>
       </c>
       <c r="O23" t="n">
-        <v>1298.380454214142</v>
+        <v>1298.380454214144</v>
       </c>
       <c r="P23" t="n">
-        <v>1417.709999999998</v>
+        <v>1417.71</v>
       </c>
       <c r="Q23" t="n">
         <v>1884</v>
@@ -6013,19 +6013,19 @@
         <v>1360.060919970324</v>
       </c>
       <c r="U23" t="n">
-        <v>1144.157083921103</v>
+        <v>1360.060919970324</v>
       </c>
       <c r="V23" t="n">
-        <v>1144.157083921103</v>
+        <v>996.5750369735322</v>
       </c>
       <c r="W23" t="n">
-        <v>1144.157083921103</v>
+        <v>624.4806167907568</v>
       </c>
       <c r="X23" t="n">
-        <v>818.6198784052774</v>
+        <v>559.4438556875434</v>
       </c>
       <c r="Y23" t="n">
-        <v>574.8648958973922</v>
+        <v>315.6888731796582</v>
       </c>
     </row>
     <row r="24">
@@ -6153,13 +6153,13 @@
         <v>808.8085128008889</v>
       </c>
       <c r="O25" t="n">
-        <v>488.4301818053614</v>
+        <v>808.8085128008889</v>
       </c>
       <c r="P25" t="n">
-        <v>488.4301818053614</v>
+        <v>808.8085128008889</v>
       </c>
       <c r="Q25" t="n">
-        <v>59.86425612293908</v>
+        <v>481.776966498596</v>
       </c>
       <c r="R25" t="n">
         <v>37.68</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>807.7018194108889</v>
+        <v>499.3941484353594</v>
       </c>
       <c r="C26" t="n">
-        <v>807.7018194108889</v>
+        <v>245.3794229373857</v>
       </c>
       <c r="D26" t="n">
-        <v>807.7018194108889</v>
+        <v>245.3794229373857</v>
       </c>
       <c r="E26" t="n">
-        <v>655.8058082331484</v>
+        <v>245.3794229373857</v>
       </c>
       <c r="F26" t="n">
-        <v>446.8263852957626</v>
+        <v>36.4</v>
       </c>
       <c r="G26" t="n">
-        <v>239.8393435967817</v>
+        <v>36.4</v>
       </c>
       <c r="H26" t="n">
         <v>36.4</v>
@@ -6217,16 +6217,16 @@
         <v>36.4</v>
       </c>
       <c r="J26" t="n">
-        <v>486.85</v>
+        <v>72.30532376710933</v>
       </c>
       <c r="K26" t="n">
-        <v>592.6579514070352</v>
+        <v>178.1132751741445</v>
       </c>
       <c r="L26" t="n">
-        <v>723.9220713065326</v>
+        <v>309.377395073642</v>
       </c>
       <c r="M26" t="n">
-        <v>1174.372071306533</v>
+        <v>729.1670721779226</v>
       </c>
       <c r="N26" t="n">
         <v>1179.617072177923</v>
@@ -6247,22 +6247,22 @@
         <v>1539.391505205356</v>
       </c>
       <c r="T26" t="n">
-        <v>1539.391505205356</v>
+        <v>1150.505038711349</v>
       </c>
       <c r="U26" t="n">
-        <v>1539.391505205356</v>
+        <v>694.7938463192193</v>
       </c>
       <c r="V26" t="n">
-        <v>1539.391505205356</v>
+        <v>499.3941484353594</v>
       </c>
       <c r="W26" t="n">
-        <v>1094.569812295308</v>
+        <v>499.3941484353594</v>
       </c>
       <c r="X26" t="n">
-        <v>1094.569812295308</v>
+        <v>499.3941484353594</v>
       </c>
       <c r="Y26" t="n">
-        <v>1094.569812295308</v>
+        <v>499.3941484353594</v>
       </c>
     </row>
     <row r="27">
@@ -6272,19 +6272,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>740.451493743955</v>
+        <v>335.9705819084108</v>
       </c>
       <c r="C27" t="n">
-        <v>740.451493743955</v>
+        <v>171.2231955998055</v>
       </c>
       <c r="D27" t="n">
-        <v>588.9992847563766</v>
+        <v>171.2231955998055</v>
       </c>
       <c r="E27" t="n">
-        <v>442.8658532190912</v>
+        <v>171.2231955998055</v>
       </c>
       <c r="F27" t="n">
-        <v>299.7989417666903</v>
+        <v>171.2231955998055</v>
       </c>
       <c r="G27" t="n">
         <v>171.2231955998055</v>
@@ -6299,22 +6299,22 @@
         <v>202.4041457413367</v>
       </c>
       <c r="K27" t="n">
-        <v>461.6931358068246</v>
+        <v>461.6931358068073</v>
       </c>
       <c r="L27" t="n">
-        <v>829.676423345421</v>
+        <v>829.6764233454037</v>
       </c>
       <c r="M27" t="n">
-        <v>1028.52291508828</v>
+        <v>1028.522915088263</v>
       </c>
       <c r="N27" t="n">
-        <v>1277.553728846792</v>
+        <v>1277.553728846774</v>
       </c>
       <c r="O27" t="n">
-        <v>1622.485301002209</v>
+        <v>1622.485301002191</v>
       </c>
       <c r="P27" t="n">
-        <v>1820.000000000017</v>
+        <v>1820</v>
       </c>
       <c r="Q27" t="n">
         <v>1820</v>
@@ -6323,25 +6323,25 @@
         <v>1820</v>
       </c>
       <c r="S27" t="n">
-        <v>1820</v>
+        <v>1582.483627352182</v>
       </c>
       <c r="T27" t="n">
-        <v>1612.378005402549</v>
+        <v>1374.861632754732</v>
       </c>
       <c r="U27" t="n">
-        <v>1575.119530157459</v>
+        <v>1170.638618321915</v>
       </c>
       <c r="V27" t="n">
-        <v>1356.42188652966</v>
+        <v>951.9409746941166</v>
       </c>
       <c r="W27" t="n">
-        <v>1356.42188652966</v>
+        <v>951.9409746941166</v>
       </c>
       <c r="X27" t="n">
-        <v>1132.318109312097</v>
+        <v>727.8371974765533</v>
       </c>
       <c r="Y27" t="n">
-        <v>928.8924600533758</v>
+        <v>524.4115482178318</v>
       </c>
     </row>
     <row r="28">
@@ -6351,16 +6351,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>141.2516460710547</v>
+        <v>64.09724610363861</v>
       </c>
       <c r="C28" t="n">
-        <v>141.2516460710547</v>
+        <v>64.09724610363861</v>
       </c>
       <c r="D28" t="n">
-        <v>141.2516460710547</v>
+        <v>64.09724610363861</v>
       </c>
       <c r="E28" t="n">
-        <v>141.2516460710547</v>
+        <v>64.09724610363861</v>
       </c>
       <c r="F28" t="n">
         <v>64.09724610363861</v>
@@ -6387,40 +6387,40 @@
         <v>256.2565761459113</v>
       </c>
       <c r="N28" t="n">
-        <v>135.0210700055814</v>
+        <v>256.2565761459113</v>
       </c>
       <c r="O28" t="n">
-        <v>135.0210700055814</v>
+        <v>256.2565761459113</v>
       </c>
       <c r="P28" t="n">
-        <v>135.0210700055814</v>
+        <v>256.2565761459113</v>
       </c>
       <c r="Q28" t="n">
-        <v>135.0210700055814</v>
+        <v>256.2565761459113</v>
       </c>
       <c r="R28" t="n">
-        <v>135.0210700055814</v>
+        <v>256.2565761459113</v>
       </c>
       <c r="S28" t="n">
-        <v>135.0210700055814</v>
+        <v>96.8571844937473</v>
       </c>
       <c r="T28" t="n">
-        <v>124.5016370385054</v>
+        <v>86.33775152667128</v>
       </c>
       <c r="U28" t="n">
-        <v>171.0931814800707</v>
+        <v>132.9292959682366</v>
       </c>
       <c r="V28" t="n">
-        <v>169.9110499485392</v>
+        <v>131.7471644367051</v>
       </c>
       <c r="W28" t="n">
-        <v>141.2516460710547</v>
+        <v>103.0877605592206</v>
       </c>
       <c r="X28" t="n">
-        <v>141.2516460710547</v>
+        <v>103.0877605592206</v>
       </c>
       <c r="Y28" t="n">
-        <v>141.2516460710547</v>
+        <v>103.0877605592206</v>
       </c>
     </row>
     <row r="29">
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>908.509872465181</v>
+        <v>456.1899737926569</v>
       </c>
       <c r="C29" t="n">
-        <v>725.2022176742781</v>
+        <v>456.1899737926569</v>
       </c>
       <c r="D29" t="n">
-        <v>581.4252926845309</v>
+        <v>312.4130488029097</v>
       </c>
       <c r="E29" t="n">
-        <v>443.6845961119362</v>
+        <v>174.672352230315</v>
       </c>
       <c r="F29" t="n">
-        <v>305.4122438816212</v>
+        <v>36.4</v>
       </c>
       <c r="G29" t="n">
-        <v>169.1322728897109</v>
+        <v>36.4</v>
       </c>
       <c r="H29" t="n">
         <v>36.4</v>
@@ -6454,25 +6454,25 @@
         <v>36.4</v>
       </c>
       <c r="J29" t="n">
-        <v>486.8500000000039</v>
+        <v>486.85</v>
       </c>
       <c r="K29" t="n">
-        <v>588.1090565269275</v>
+        <v>588.1090565269087</v>
       </c>
       <c r="L29" t="n">
-        <v>719.3731764264251</v>
+        <v>719.3731764264062</v>
       </c>
       <c r="M29" t="n">
-        <v>1169.823176426429</v>
+        <v>1169.823176426406</v>
       </c>
       <c r="N29" t="n">
-        <v>1179.617072177919</v>
+        <v>1179.617072177923</v>
       </c>
       <c r="O29" t="n">
-        <v>1250.22045421414</v>
+        <v>1250.220454214144</v>
       </c>
       <c r="P29" t="n">
-        <v>1369.549999999996</v>
+        <v>1369.55</v>
       </c>
       <c r="Q29" t="n">
         <v>1820</v>
@@ -6487,19 +6487,19 @@
         <v>1292.02051592992</v>
       </c>
       <c r="U29" t="n">
-        <v>1292.02051592992</v>
+        <v>907.0163942448605</v>
       </c>
       <c r="V29" t="n">
-        <v>1292.02051592992</v>
+        <v>701.9651583207442</v>
       </c>
       <c r="W29" t="n">
-        <v>1292.02051592992</v>
+        <v>701.9651583207442</v>
       </c>
       <c r="X29" t="n">
-        <v>1292.02051592992</v>
+        <v>701.9651583207442</v>
       </c>
       <c r="Y29" t="n">
-        <v>1124.670794642529</v>
+        <v>456.1899737926569</v>
       </c>
     </row>
     <row r="30">
@@ -6545,13 +6545,13 @@
         <v>1030.292830456798</v>
       </c>
       <c r="N30" t="n">
-        <v>1277.553728846791</v>
+        <v>1279.32364421531</v>
       </c>
       <c r="O30" t="n">
-        <v>1622.485301002208</v>
+        <v>1622.485301002191</v>
       </c>
       <c r="P30" t="n">
-        <v>1820.000000000017</v>
+        <v>1820</v>
       </c>
       <c r="Q30" t="n">
         <v>1820</v>
@@ -6572,13 +6572,13 @@
         <v>955.5418955671963</v>
       </c>
       <c r="W30" t="n">
-        <v>881.1202266739538</v>
+        <v>789.5084178805008</v>
       </c>
       <c r="X30" t="n">
-        <v>727.7235201634612</v>
+        <v>636.1117113700084</v>
       </c>
       <c r="Y30" t="n">
-        <v>595.0049416118103</v>
+        <v>503.3931328183575</v>
       </c>
     </row>
     <row r="31">
@@ -6588,52 +6588,52 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>302.0157087577843</v>
+        <v>340.984550360351</v>
       </c>
       <c r="C31" t="n">
-        <v>297.242732345618</v>
+        <v>340.984550360351</v>
       </c>
       <c r="D31" t="n">
-        <v>279.5293807743498</v>
+        <v>340.984550360351</v>
       </c>
       <c r="E31" t="n">
-        <v>266.417355686515</v>
+        <v>340.984550360351</v>
       </c>
       <c r="F31" t="n">
-        <v>259.9700264261696</v>
+        <v>340.984550360351</v>
       </c>
       <c r="G31" t="n">
-        <v>283.0697087064975</v>
+        <v>364.0842326406789</v>
       </c>
       <c r="H31" t="n">
-        <v>325.2236378003213</v>
+        <v>406.2381617345027</v>
       </c>
       <c r="I31" t="n">
-        <v>426.8971442773878</v>
+        <v>507.9116682115692</v>
       </c>
       <c r="J31" t="n">
-        <v>683.6802139462326</v>
+        <v>764.694737880414</v>
       </c>
       <c r="K31" t="n">
-        <v>706.7139888667075</v>
+        <v>787.7285128008889</v>
       </c>
       <c r="L31" t="n">
-        <v>606.1937153508186</v>
+        <v>787.7285128008889</v>
       </c>
       <c r="M31" t="n">
-        <v>410.6854971763602</v>
+        <v>787.7285128008889</v>
       </c>
       <c r="N31" t="n">
-        <v>162.6942305498859</v>
+        <v>787.7285128008889</v>
       </c>
       <c r="O31" t="n">
-        <v>162.6942305498859</v>
+        <v>787.7285128008889</v>
       </c>
       <c r="P31" t="n">
-        <v>162.6942305498859</v>
+        <v>787.7285128008889</v>
       </c>
       <c r="Q31" t="n">
-        <v>162.6942305498859</v>
+        <v>571.2094894638913</v>
       </c>
       <c r="R31" t="n">
         <v>125.0923209450933</v>
@@ -6657,7 +6657,7 @@
         <v>340.984550360351</v>
       </c>
       <c r="Y31" t="n">
-        <v>321.3225777851365</v>
+        <v>340.984550360351</v>
       </c>
     </row>
     <row r="32">
@@ -6667,22 +6667,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>36.4</v>
+        <v>581.4252926845309</v>
       </c>
       <c r="C32" t="n">
-        <v>36.4</v>
+        <v>581.4252926845309</v>
       </c>
       <c r="D32" t="n">
-        <v>36.4</v>
+        <v>581.4252926845309</v>
       </c>
       <c r="E32" t="n">
-        <v>36.4</v>
+        <v>443.6845961119362</v>
       </c>
       <c r="F32" t="n">
-        <v>36.4</v>
+        <v>305.4122438816212</v>
       </c>
       <c r="G32" t="n">
-        <v>36.4</v>
+        <v>169.1322728897109</v>
       </c>
       <c r="H32" t="n">
         <v>36.4</v>
@@ -6691,25 +6691,25 @@
         <v>36.4</v>
       </c>
       <c r="J32" t="n">
-        <v>486.8500000000039</v>
+        <v>72.30532376710933</v>
       </c>
       <c r="K32" t="n">
-        <v>708.7123175815644</v>
+        <v>178.1132751741445</v>
       </c>
       <c r="L32" t="n">
-        <v>1159.162317581564</v>
+        <v>304.8285001935157</v>
       </c>
       <c r="M32" t="n">
-        <v>1159.162317581564</v>
+        <v>729.1670721779226</v>
       </c>
       <c r="N32" t="n">
-        <v>1179.617072177919</v>
+        <v>1179.617072177923</v>
       </c>
       <c r="O32" t="n">
-        <v>1250.22045421414</v>
+        <v>1250.220454214144</v>
       </c>
       <c r="P32" t="n">
-        <v>1369.549999999996</v>
+        <v>1369.55</v>
       </c>
       <c r="Q32" t="n">
         <v>1820</v>
@@ -6721,22 +6721,22 @@
         <v>1820</v>
       </c>
       <c r="T32" t="n">
-        <v>1820</v>
+        <v>1501.820604213064</v>
       </c>
       <c r="U32" t="n">
-        <v>1434.995878314941</v>
+        <v>1116.816482528005</v>
       </c>
       <c r="V32" t="n">
-        <v>1069.489793297947</v>
+        <v>751.3103975110109</v>
       </c>
       <c r="W32" t="n">
-        <v>695.3751710949695</v>
+        <v>751.3103975110109</v>
       </c>
       <c r="X32" t="n">
-        <v>367.8177635589415</v>
+        <v>751.3103975110109</v>
       </c>
       <c r="Y32" t="n">
-        <v>252.560922177348</v>
+        <v>581.4252926845309</v>
       </c>
     </row>
     <row r="33">
@@ -6746,22 +6746,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>385.6592372160074</v>
+        <v>477.2710460094602</v>
       </c>
       <c r="C33" t="n">
-        <v>291.6189216144728</v>
+        <v>383.2307304079255</v>
       </c>
       <c r="D33" t="n">
-        <v>210.873783333965</v>
+        <v>302.4855921274178</v>
       </c>
       <c r="E33" t="n">
-        <v>154.6993905518729</v>
+        <v>227.059231297203</v>
       </c>
       <c r="F33" t="n">
         <v>154.6993905518729</v>
       </c>
       <c r="G33" t="n">
-        <v>96.83071509205871</v>
+        <v>96.83071509205868</v>
       </c>
       <c r="H33" t="n">
         <v>36.4</v>
@@ -6782,7 +6782,7 @@
         <v>1030.292830456798</v>
       </c>
       <c r="N33" t="n">
-        <v>1277.553728846774</v>
+        <v>1279.32364421531</v>
       </c>
       <c r="O33" t="n">
         <v>1622.485301002191</v>
@@ -6794,28 +6794,28 @@
         <v>1820</v>
       </c>
       <c r="R33" t="n">
-        <v>1566.098546664835</v>
+        <v>1657.710355458288</v>
       </c>
       <c r="S33" t="n">
-        <v>1373.96333610405</v>
+        <v>1465.575144897503</v>
       </c>
       <c r="T33" t="n">
-        <v>1237.04841221367</v>
+        <v>1328.660221007123</v>
       </c>
       <c r="U33" t="n">
-        <v>1103.532468487924</v>
+        <v>1195.144277281377</v>
       </c>
       <c r="V33" t="n">
-        <v>955.5418955671963</v>
+        <v>1047.153704360649</v>
       </c>
       <c r="W33" t="n">
-        <v>789.5084178805008</v>
+        <v>881.1202266739538</v>
       </c>
       <c r="X33" t="n">
-        <v>636.1117113700084</v>
+        <v>727.7235201634612</v>
       </c>
       <c r="Y33" t="n">
-        <v>503.3931328183575</v>
+        <v>595.0049416118103</v>
       </c>
     </row>
     <row r="34">
@@ -6825,55 +6825,55 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>302.0157087577843</v>
+        <v>340.984550360351</v>
       </c>
       <c r="C34" t="n">
-        <v>297.242732345618</v>
+        <v>340.984550360351</v>
       </c>
       <c r="D34" t="n">
-        <v>279.5293807743498</v>
+        <v>340.984550360351</v>
       </c>
       <c r="E34" t="n">
-        <v>266.417355686515</v>
+        <v>340.984550360351</v>
       </c>
       <c r="F34" t="n">
-        <v>259.9700264261696</v>
+        <v>340.984550360351</v>
       </c>
       <c r="G34" t="n">
-        <v>283.0697087064975</v>
+        <v>364.0842326406789</v>
       </c>
       <c r="H34" t="n">
-        <v>325.2236378003213</v>
+        <v>406.2381617345027</v>
       </c>
       <c r="I34" t="n">
-        <v>426.8971442773878</v>
+        <v>507.9116682115692</v>
       </c>
       <c r="J34" t="n">
-        <v>683.6802139462326</v>
+        <v>764.694737880414</v>
       </c>
       <c r="K34" t="n">
-        <v>706.7139888667075</v>
+        <v>787.7285128008889</v>
       </c>
       <c r="L34" t="n">
-        <v>706.7139888667075</v>
+        <v>787.7285128008889</v>
       </c>
       <c r="M34" t="n">
-        <v>706.7139888667075</v>
+        <v>787.7285128008889</v>
       </c>
       <c r="N34" t="n">
-        <v>706.7139888667075</v>
+        <v>787.7285128008889</v>
       </c>
       <c r="O34" t="n">
-        <v>706.7139888667075</v>
+        <v>787.7285128008889</v>
       </c>
       <c r="P34" t="n">
-        <v>706.7139888667075</v>
+        <v>410.0867552743957</v>
       </c>
       <c r="Q34" t="n">
-        <v>571.2094894638913</v>
+        <v>36.4</v>
       </c>
       <c r="R34" t="n">
-        <v>125.0923209450933</v>
+        <v>36.4</v>
       </c>
       <c r="S34" t="n">
         <v>36.4</v>
@@ -6894,7 +6894,7 @@
         <v>340.984550360351</v>
       </c>
       <c r="Y34" t="n">
-        <v>321.3225777851365</v>
+        <v>340.984550360351</v>
       </c>
     </row>
     <row r="35">
@@ -6904,22 +6904,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>742.7018603250275</v>
+        <v>357.9800070212179</v>
       </c>
       <c r="C35" t="n">
-        <v>725.2022176742781</v>
+        <v>174.672352230315</v>
       </c>
       <c r="D35" t="n">
-        <v>581.4252926845309</v>
+        <v>174.672352230315</v>
       </c>
       <c r="E35" t="n">
-        <v>443.6845961119362</v>
+        <v>174.672352230315</v>
       </c>
       <c r="F35" t="n">
-        <v>305.4122438816212</v>
+        <v>36.4</v>
       </c>
       <c r="G35" t="n">
-        <v>169.1322728897109</v>
+        <v>36.4</v>
       </c>
       <c r="H35" t="n">
         <v>36.4</v>
@@ -6928,25 +6928,25 @@
         <v>36.4</v>
       </c>
       <c r="J35" t="n">
-        <v>72.30532376710933</v>
+        <v>486.85</v>
       </c>
       <c r="K35" t="n">
-        <v>522.7553237671093</v>
+        <v>592.6579514070352</v>
       </c>
       <c r="L35" t="n">
-        <v>791.9929674934515</v>
+        <v>719.3731764264062</v>
       </c>
       <c r="M35" t="n">
-        <v>1179.617072177919</v>
+        <v>1169.823176426406</v>
       </c>
       <c r="N35" t="n">
-        <v>1630.067072177923</v>
+        <v>1179.617072177923</v>
       </c>
       <c r="O35" t="n">
-        <v>1700.670454214144</v>
+        <v>1250.220454214144</v>
       </c>
       <c r="P35" t="n">
-        <v>1820</v>
+        <v>1369.55</v>
       </c>
       <c r="Q35" t="n">
         <v>1820</v>
@@ -6955,25 +6955,25 @@
         <v>1820</v>
       </c>
       <c r="S35" t="n">
-        <v>1820</v>
+        <v>1800.784231713184</v>
       </c>
       <c r="T35" t="n">
-        <v>1501.820604213064</v>
+        <v>1482.604835926248</v>
       </c>
       <c r="U35" t="n">
-        <v>1116.816482528005</v>
+        <v>1097.600714241189</v>
       </c>
       <c r="V35" t="n">
-        <v>1116.816482528005</v>
+        <v>732.0946292241953</v>
       </c>
       <c r="W35" t="n">
-        <v>742.7018603250275</v>
+        <v>357.9800070212179</v>
       </c>
       <c r="X35" t="n">
-        <v>742.7018603250275</v>
+        <v>357.9800070212179</v>
       </c>
       <c r="Y35" t="n">
-        <v>742.7018603250275</v>
+        <v>357.9800070212179</v>
       </c>
     </row>
     <row r="36">
@@ -7019,19 +7019,19 @@
         <v>1030.292830456798</v>
       </c>
       <c r="N36" t="n">
-        <v>1277.553728846791</v>
+        <v>1279.32364421531</v>
       </c>
       <c r="O36" t="n">
-        <v>1622.485301002208</v>
+        <v>1622.485301002191</v>
       </c>
       <c r="P36" t="n">
-        <v>1820.000000000017</v>
+        <v>1820</v>
       </c>
       <c r="Q36" t="n">
         <v>1820</v>
       </c>
       <c r="R36" t="n">
-        <v>1657.710355458288</v>
+        <v>1566.098546664835</v>
       </c>
       <c r="S36" t="n">
         <v>1465.575144897503</v>
@@ -7062,49 +7062,49 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>340.984550360351</v>
+        <v>302.0157087577843</v>
       </c>
       <c r="C37" t="n">
-        <v>340.984550360351</v>
+        <v>302.0157087577843</v>
       </c>
       <c r="D37" t="n">
-        <v>340.984550360351</v>
+        <v>302.0157087577843</v>
       </c>
       <c r="E37" t="n">
-        <v>340.984550360351</v>
+        <v>302.0157087577843</v>
       </c>
       <c r="F37" t="n">
-        <v>340.984550360351</v>
+        <v>302.0157087577843</v>
       </c>
       <c r="G37" t="n">
-        <v>364.0842326406789</v>
+        <v>325.1153910381122</v>
       </c>
       <c r="H37" t="n">
-        <v>406.2381617345027</v>
+        <v>367.269320131936</v>
       </c>
       <c r="I37" t="n">
-        <v>507.9116682115692</v>
+        <v>468.9428266090025</v>
       </c>
       <c r="J37" t="n">
-        <v>764.694737880414</v>
+        <v>725.7258962778473</v>
       </c>
       <c r="K37" t="n">
-        <v>787.7285128008889</v>
+        <v>748.7596711983222</v>
       </c>
       <c r="L37" t="n">
-        <v>787.7285128008889</v>
+        <v>748.7596711983222</v>
       </c>
       <c r="M37" t="n">
-        <v>787.7285128008889</v>
+        <v>748.7596711983222</v>
       </c>
       <c r="N37" t="n">
-        <v>787.7285128008889</v>
+        <v>748.7596711983222</v>
       </c>
       <c r="O37" t="n">
-        <v>787.7285128008889</v>
+        <v>748.7596711983222</v>
       </c>
       <c r="P37" t="n">
-        <v>787.7285128008889</v>
+        <v>748.7596711983222</v>
       </c>
       <c r="Q37" t="n">
         <v>571.2094894638913</v>
@@ -7131,7 +7131,7 @@
         <v>340.984550360351</v>
       </c>
       <c r="Y37" t="n">
-        <v>340.984550360351</v>
+        <v>321.3225777851365</v>
       </c>
     </row>
     <row r="38">
@@ -7156,7 +7156,7 @@
         <v>305.4122438816212</v>
       </c>
       <c r="G38" t="n">
-        <v>169.132272889711</v>
+        <v>169.1322728897109</v>
       </c>
       <c r="H38" t="n">
         <v>36.4</v>
@@ -7165,43 +7165,43 @@
         <v>36.4</v>
       </c>
       <c r="J38" t="n">
-        <v>72.30532376710933</v>
+        <v>486.85</v>
       </c>
       <c r="K38" t="n">
-        <v>173.5643802940576</v>
+        <v>592.6579514070352</v>
       </c>
       <c r="L38" t="n">
-        <v>304.8285001935551</v>
+        <v>719.3731764264064</v>
       </c>
       <c r="M38" t="n">
-        <v>729.1670721779305</v>
+        <v>1169.823176426406</v>
       </c>
       <c r="N38" t="n">
-        <v>1179.617072177934</v>
+        <v>1179.617072177923</v>
       </c>
       <c r="O38" t="n">
-        <v>1250.220454214156</v>
+        <v>1250.220454214144</v>
       </c>
       <c r="P38" t="n">
-        <v>1369.550000000012</v>
+        <v>1369.55</v>
       </c>
       <c r="Q38" t="n">
-        <v>1820.000000000016</v>
+        <v>1820</v>
       </c>
       <c r="R38" t="n">
         <v>1820</v>
       </c>
       <c r="S38" t="n">
-        <v>1820</v>
+        <v>1610.199911716856</v>
       </c>
       <c r="T38" t="n">
-        <v>1820</v>
+        <v>1610.199911716856</v>
       </c>
       <c r="U38" t="n">
-        <v>1610.181902204186</v>
+        <v>1236.067280001209</v>
       </c>
       <c r="V38" t="n">
-        <v>1610.181902204186</v>
+        <v>1236.067280001209</v>
       </c>
       <c r="W38" t="n">
         <v>1236.067280001209</v>
@@ -7247,22 +7247,22 @@
         <v>202.4041457413367</v>
       </c>
       <c r="K39" t="n">
-        <v>461.6931358068228</v>
+        <v>461.6931358068073</v>
       </c>
       <c r="L39" t="n">
-        <v>829.6764233454192</v>
+        <v>829.6764233454037</v>
       </c>
       <c r="M39" t="n">
-        <v>1028.522915088278</v>
+        <v>1028.522915088263</v>
       </c>
       <c r="N39" t="n">
-        <v>1277.55372884679</v>
+        <v>1277.553728846774</v>
       </c>
       <c r="O39" t="n">
-        <v>1622.485301002207</v>
+        <v>1622.485301002191</v>
       </c>
       <c r="P39" t="n">
-        <v>1820.000000000016</v>
+        <v>1820</v>
       </c>
       <c r="Q39" t="n">
         <v>1820</v>
@@ -7329,16 +7329,16 @@
         <v>787.7285128008889</v>
       </c>
       <c r="L40" t="n">
-        <v>787.7285128008889</v>
+        <v>687.208239285</v>
       </c>
       <c r="M40" t="n">
-        <v>787.7285128008889</v>
+        <v>491.7000211105416</v>
       </c>
       <c r="N40" t="n">
-        <v>539.7372461744146</v>
+        <v>243.7087544840673</v>
       </c>
       <c r="O40" t="n">
-        <v>217.338713158685</v>
+        <v>36.4</v>
       </c>
       <c r="P40" t="n">
         <v>36.4</v>
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>898.2300506573907</v>
+        <v>613.9826262525282</v>
       </c>
       <c r="C41" t="n">
-        <v>898.2300506573907</v>
+        <v>613.9826262525282</v>
       </c>
       <c r="D41" t="n">
-        <v>898.2300506573907</v>
+        <v>613.9826262525282</v>
       </c>
       <c r="E41" t="n">
-        <v>898.2300506573907</v>
+        <v>613.9826262525282</v>
       </c>
       <c r="F41" t="n">
-        <v>608.4425469119242</v>
+        <v>324.1951225070617</v>
       </c>
       <c r="G41" t="n">
-        <v>320.6474244048624</v>
+        <v>36.4</v>
       </c>
       <c r="H41" t="n">
         <v>36.4</v>
@@ -7402,25 +7402,25 @@
         <v>36.4</v>
       </c>
       <c r="J41" t="n">
-        <v>486.8500000000039</v>
+        <v>486.85</v>
       </c>
       <c r="K41" t="n">
-        <v>592.6579514070391</v>
+        <v>592.6579514070352</v>
       </c>
       <c r="L41" t="n">
-        <v>723.9220713065366</v>
+        <v>723.9220713065326</v>
       </c>
       <c r="M41" t="n">
-        <v>729.1670721779149</v>
+        <v>1174.372071306533</v>
       </c>
       <c r="N41" t="n">
-        <v>1179.617072177919</v>
+        <v>1624.822071306533</v>
       </c>
       <c r="O41" t="n">
-        <v>1250.22045421414</v>
+        <v>1695.425453342754</v>
       </c>
       <c r="P41" t="n">
-        <v>1369.549999999996</v>
+        <v>1814.75499912861</v>
       </c>
       <c r="Q41" t="n">
         <v>1820</v>
@@ -7429,25 +7429,25 @@
         <v>1739.09058338749</v>
       </c>
       <c r="S41" t="n">
-        <v>1739.09058338749</v>
+        <v>1377.775343589194</v>
       </c>
       <c r="T41" t="n">
-        <v>1739.09058338749</v>
+        <v>1073.578585848491</v>
       </c>
       <c r="U41" t="n">
-        <v>1295.52038670063</v>
+        <v>613.9826262525282</v>
       </c>
       <c r="V41" t="n">
-        <v>1295.52038670063</v>
+        <v>613.9826262525282</v>
       </c>
       <c r="W41" t="n">
-        <v>1295.52038670063</v>
+        <v>613.9826262525282</v>
       </c>
       <c r="X41" t="n">
-        <v>1295.52038670063</v>
+        <v>613.9826262525282</v>
       </c>
       <c r="Y41" t="n">
-        <v>898.2300506573907</v>
+        <v>613.9826262525282</v>
       </c>
     </row>
     <row r="42">
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>353.1537804044161</v>
+        <v>981.4861275747984</v>
       </c>
       <c r="C42" t="n">
-        <v>353.1537804044161</v>
+        <v>735.9306604581122</v>
       </c>
       <c r="D42" t="n">
-        <v>120.8934906087568</v>
+        <v>503.670370662453</v>
       </c>
       <c r="E42" t="n">
-        <v>120.8934906087568</v>
+        <v>503.670370662453</v>
       </c>
       <c r="F42" t="n">
-        <v>120.8934906087568</v>
+        <v>279.7953784019713</v>
       </c>
       <c r="G42" t="n">
-        <v>120.8934906087568</v>
+        <v>279.7953784019713</v>
       </c>
       <c r="H42" t="n">
-        <v>120.8934906087568</v>
+        <v>67.8495117947611</v>
       </c>
       <c r="I42" t="n">
         <v>36.4</v>
@@ -7487,13 +7487,13 @@
         <v>463.4630511753427</v>
       </c>
       <c r="L42" t="n">
-        <v>829.6764233454037</v>
+        <v>831.4463387139391</v>
       </c>
       <c r="M42" t="n">
-        <v>1028.522915088263</v>
+        <v>1030.292830456798</v>
       </c>
       <c r="N42" t="n">
-        <v>1277.553728846774</v>
+        <v>1279.32364421531</v>
       </c>
       <c r="O42" t="n">
         <v>1622.485301002191</v>
@@ -7502,31 +7502,31 @@
         <v>1820</v>
       </c>
       <c r="Q42" t="n">
-        <v>1820.000000000019</v>
+        <v>1820</v>
       </c>
       <c r="R42" t="n">
-        <v>1800.28158062987</v>
+        <v>1820</v>
       </c>
       <c r="S42" t="n">
-        <v>1800.28158062987</v>
+        <v>1820</v>
       </c>
       <c r="T42" t="n">
-        <v>1511.851505224338</v>
+        <v>1820</v>
       </c>
       <c r="U42" t="n">
-        <v>1226.820409983441</v>
+        <v>1534.968904759102</v>
       </c>
       <c r="V42" t="n">
-        <v>927.3146855475618</v>
+        <v>1534.968904759102</v>
       </c>
       <c r="W42" t="n">
-        <v>927.3146855475618</v>
+        <v>1534.968904759102</v>
       </c>
       <c r="X42" t="n">
-        <v>622.4028275219177</v>
+        <v>1534.968904759102</v>
       </c>
       <c r="Y42" t="n">
-        <v>622.4028275219177</v>
+        <v>1250.7351746923</v>
       </c>
     </row>
     <row r="43">
@@ -7578,25 +7578,25 @@
         <v>144.6830696688448</v>
       </c>
       <c r="P43" t="n">
-        <v>69.67053929031188</v>
+        <v>144.6830696688448</v>
       </c>
       <c r="Q43" t="n">
-        <v>69.67053929031188</v>
+        <v>144.6830696688448</v>
       </c>
       <c r="R43" t="n">
-        <v>69.67053929031188</v>
+        <v>144.6830696688448</v>
       </c>
       <c r="S43" t="n">
-        <v>69.67053929031188</v>
+        <v>144.6830696688448</v>
       </c>
       <c r="T43" t="n">
-        <v>69.67053929031188</v>
+        <v>144.6830696688448</v>
       </c>
       <c r="U43" t="n">
-        <v>36.4</v>
+        <v>111.4125303785329</v>
       </c>
       <c r="V43" t="n">
-        <v>36.4</v>
+        <v>111.4125303785329</v>
       </c>
       <c r="W43" t="n">
         <v>36.4</v>
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>155.278091349953</v>
+        <v>558.7174349467347</v>
       </c>
       <c r="C44" t="n">
-        <v>155.278091349953</v>
+        <v>558.7174349467347</v>
       </c>
       <c r="D44" t="n">
-        <v>155.278091349953</v>
+        <v>558.7174349467347</v>
       </c>
       <c r="E44" t="n">
-        <v>155.278091349953</v>
+        <v>558.7174349467347</v>
       </c>
       <c r="F44" t="n">
-        <v>155.278091349953</v>
+        <v>558.7174349467347</v>
       </c>
       <c r="G44" t="n">
-        <v>155.278091349953</v>
+        <v>558.7174349467347</v>
       </c>
       <c r="H44" t="n">
         <v>155.278091349953</v>
@@ -7639,52 +7639,52 @@
         <v>36.4</v>
       </c>
       <c r="J44" t="n">
-        <v>486.85</v>
+        <v>72.30532376710933</v>
       </c>
       <c r="K44" t="n">
-        <v>937.3</v>
+        <v>178.1132751741445</v>
       </c>
       <c r="L44" t="n">
-        <v>1068.564119899497</v>
+        <v>309.377395073642</v>
       </c>
       <c r="M44" t="n">
-        <v>1519.014119899498</v>
+        <v>729.1670721779226</v>
       </c>
       <c r="N44" t="n">
-        <v>1630.067072177923</v>
+        <v>1179.617072177923</v>
       </c>
       <c r="O44" t="n">
-        <v>1700.670454214144</v>
+        <v>1250.220454214144</v>
       </c>
       <c r="P44" t="n">
-        <v>1820</v>
+        <v>1369.55</v>
       </c>
       <c r="Q44" t="n">
         <v>1820</v>
       </c>
       <c r="R44" t="n">
-        <v>1820</v>
+        <v>1619.898664195571</v>
       </c>
       <c r="S44" t="n">
-        <v>1820</v>
+        <v>1160.30270459961</v>
       </c>
       <c r="T44" t="n">
-        <v>1820</v>
+        <v>700.7067450036482</v>
       </c>
       <c r="U44" t="n">
-        <v>1360.404040404024</v>
+        <v>700.7067450036482</v>
       </c>
       <c r="V44" t="n">
-        <v>1074.470010541903</v>
+        <v>700.7067450036482</v>
       </c>
       <c r="W44" t="n">
-        <v>614.8740509459277</v>
+        <v>700.7067450036482</v>
       </c>
       <c r="X44" t="n">
-        <v>155.278091349953</v>
+        <v>700.7067450036482</v>
       </c>
       <c r="Y44" t="n">
-        <v>155.278091349953</v>
+        <v>700.7067450036482</v>
       </c>
     </row>
     <row r="45">
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>568.6611559675609</v>
+        <v>1090.347729298292</v>
       </c>
       <c r="C45" t="n">
-        <v>568.6611559675609</v>
+        <v>725.6003429896864</v>
       </c>
       <c r="D45" t="n">
-        <v>568.6611559675609</v>
+        <v>725.6003429896864</v>
       </c>
       <c r="E45" t="n">
-        <v>568.6611559675609</v>
+        <v>379.4669114524009</v>
       </c>
       <c r="F45" t="n">
-        <v>568.6611559675609</v>
+        <v>36.4</v>
       </c>
       <c r="G45" t="n">
-        <v>240.0854098006761</v>
+        <v>36.4</v>
       </c>
       <c r="H45" t="n">
-        <v>240.0854098006761</v>
+        <v>36.4</v>
       </c>
       <c r="I45" t="n">
         <v>36.4</v>
@@ -7721,7 +7721,7 @@
         <v>202.4041457413367</v>
       </c>
       <c r="K45" t="n">
-        <v>461.6931358068073</v>
+        <v>463.4630511753427</v>
       </c>
       <c r="L45" t="n">
         <v>829.6764233454037</v>
@@ -7739,31 +7739,31 @@
         <v>1820</v>
       </c>
       <c r="Q45" t="n">
-        <v>1703.136400804357</v>
+        <v>1820</v>
       </c>
       <c r="R45" t="n">
-        <v>1464.997663957304</v>
+        <v>1820</v>
       </c>
       <c r="S45" t="n">
-        <v>1005.401704361327</v>
+        <v>1820</v>
       </c>
       <c r="T45" t="n">
-        <v>1005.401704361327</v>
+        <v>1820</v>
       </c>
       <c r="U45" t="n">
-        <v>1005.401704361327</v>
+        <v>1820</v>
       </c>
       <c r="V45" t="n">
-        <v>1005.401704361327</v>
+        <v>1820</v>
       </c>
       <c r="W45" t="n">
-        <v>568.6611559675609</v>
+        <v>1820</v>
       </c>
       <c r="X45" t="n">
-        <v>568.6611559675609</v>
+        <v>1820</v>
       </c>
       <c r="Y45" t="n">
-        <v>568.6611559675609</v>
+        <v>1416.574350741279</v>
       </c>
     </row>
     <row r="46">
@@ -7967,10 +7967,10 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>364.1232814070352</v>
       </c>
       <c r="L2" t="n">
-        <v>22.25381525684935</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>867.7301829186993</v>
@@ -7985,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>553.0904280460784</v>
+        <v>211.2209618958923</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>364.1232814070352</v>
       </c>
       <c r="L5" t="n">
-        <v>338.4099798994973</v>
+        <v>240.2925285830021</v>
       </c>
       <c r="M5" t="n">
-        <v>396.7301829186992</v>
+        <v>867.7301829186993</v>
       </c>
       <c r="N5" t="n">
-        <v>798.3297922406895</v>
+        <v>327.3297922406895</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>350.4651052668121</v>
       </c>
       <c r="Q5" t="n">
-        <v>277.6295268172736</v>
+        <v>91.4633280460783</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8447,13 +8447,13 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>867.7301829186993</v>
+        <v>396.7301829186992</v>
       </c>
       <c r="N8" t="n">
-        <v>390.2788709113821</v>
+        <v>798.3297922406895</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>62.94907867069247</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -8678,16 +8678,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>364.1232814070352</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>338.4099798994976</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>396.7301829186992</v>
+        <v>867.7301829186993</v>
       </c>
       <c r="N11" t="n">
-        <v>591.8753065745464</v>
+        <v>798.3297922406895</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>82.09042804607837</v>
+        <v>107.1692036864678</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8915,7 +8915,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>333.9060329620761</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>867.7301829186993</v>
       </c>
       <c r="N14" t="n">
-        <v>798.3297922406895</v>
+        <v>490.1160674606361</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>107.7827362281006</v>
+        <v>82.09042804607837</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,19 +9149,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>364.1232814070352</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>488.6039462798415</v>
+        <v>867.7301829186993</v>
       </c>
       <c r="N17" t="n">
-        <v>798.3297922406906</v>
+        <v>353.0221004227109</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9386,19 +9386,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>333.9060329621014</v>
+        <v>25.69230818202187</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>867.7301829187008</v>
+        <v>396.7301829186992</v>
       </c>
       <c r="N20" t="n">
-        <v>798.3297922406912</v>
+        <v>798.3297922406895</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>204.1814398521526</v>
+        <v>553.0904280460784</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9626,16 +9626,16 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>333.906032962076</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>338.4099798994974</v>
       </c>
       <c r="M23" t="n">
-        <v>867.7301829187015</v>
+        <v>514.3172477873808</v>
       </c>
       <c r="N23" t="n">
-        <v>449.420804046788</v>
+        <v>798.3297922406895</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>553.0904280460808</v>
+        <v>553.0904280460784</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,7 +9860,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>418.7319961948391</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -9869,10 +9869,10 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>851.7301829186993</v>
+        <v>820.7601597917098</v>
       </c>
       <c r="N26" t="n">
-        <v>332.6277729188611</v>
+        <v>782.3297922406895</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -9942,7 +9942,7 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K27" t="n">
-        <v>294.0924475614801</v>
+        <v>294.0924475614626</v>
       </c>
       <c r="L27" t="n">
         <v>388.0893364597981</v>
@@ -10097,7 +10097,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>418.7319961948431</v>
+        <v>418.7319961948391</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -10106,10 +10106,10 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>851.7301829187031</v>
+        <v>851.7301829186993</v>
       </c>
       <c r="N29" t="n">
-        <v>337.2226162320933</v>
+        <v>337.2226162321203</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>537.0904280460824</v>
+        <v>537.0904280460784</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10188,10 +10188,10 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N30" t="n">
-        <v>483.6207338698161</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O30" t="n">
-        <v>382.6817988009037</v>
+        <v>380.8940054993526</v>
       </c>
       <c r="P30" t="n">
         <v>219.1507118405495</v>
@@ -10334,19 +10334,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>418.7319961948431</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>121.8214758127801</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>322.4099798994974</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>396.7301829186992</v>
+        <v>825.3550031049687</v>
       </c>
       <c r="N32" t="n">
-        <v>347.9911605198354</v>
+        <v>782.3297922406895</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>537.0904280460824</v>
+        <v>537.0904280460784</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10425,10 +10425,10 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N33" t="n">
-        <v>483.6207338697992</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O33" t="n">
-        <v>382.6817988009037</v>
+        <v>380.8940054993526</v>
       </c>
       <c r="P33" t="n">
         <v>219.1507118405495</v>
@@ -10571,19 +10571,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>418.7319961948391</v>
       </c>
       <c r="K35" t="n">
-        <v>348.1232814070352</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>143.0097471885761</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>788.2696825999793</v>
+        <v>851.7301829186993</v>
       </c>
       <c r="N35" t="n">
-        <v>782.3297922406935</v>
+        <v>337.2226162321203</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>82.09042804607837</v>
+        <v>537.0904280460784</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10665,7 +10665,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O36" t="n">
-        <v>382.6817988009037</v>
+        <v>380.8940054993526</v>
       </c>
       <c r="P36" t="n">
         <v>219.1507118405495</v>
@@ -10808,7 +10808,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>418.7319961948391</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -10817,10 +10817,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>825.3550031049369</v>
+        <v>851.7301829186993</v>
       </c>
       <c r="N38" t="n">
-        <v>782.3297922406935</v>
+        <v>337.2226162321199</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>537.0904280460824</v>
+        <v>537.0904280460784</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -10890,7 +10890,7 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K39" t="n">
-        <v>294.0924475614783</v>
+        <v>294.0924475614626</v>
       </c>
       <c r="L39" t="n">
         <v>388.0893364597981</v>
@@ -11045,7 +11045,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>418.7319961948431</v>
+        <v>418.7319961948391</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -11054,10 +11054,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>402.028163596859</v>
+        <v>851.7301829186993</v>
       </c>
       <c r="N41" t="n">
-        <v>782.3297922406935</v>
+        <v>782.3297922406895</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>537.0904280460824</v>
+        <v>87.38840872425004</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11130,7 +11130,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L42" t="n">
-        <v>386.3015431582472</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M42" t="n">
         <v>471.6948204301074</v>
@@ -11139,7 +11139,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O42" t="n">
-        <v>382.6817988009037</v>
+        <v>380.8940054993526</v>
       </c>
       <c r="P42" t="n">
         <v>219.1507118405495</v>
@@ -11282,19 +11282,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>418.7319961948391</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>348.1232814070352</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>851.7301829186993</v>
+        <v>820.7601597917098</v>
       </c>
       <c r="N44" t="n">
-        <v>439.5044915118258</v>
+        <v>782.3297922406895</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>82.09042804607837</v>
+        <v>537.0904280460784</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11364,10 +11364,10 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K45" t="n">
-        <v>294.0924475614626</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L45" t="n">
-        <v>388.0893364597981</v>
+        <v>386.3015431582472</v>
       </c>
       <c r="M45" t="n">
         <v>471.6948204301074</v>
@@ -22518,22 +22518,22 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2.917171281991102</v>
       </c>
       <c r="H2" t="n">
-        <v>5.208822684937445</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>117.6893104364534</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -22560,10 +22560,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>105.0978123942879</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>75.70208740031285</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -22591,28 +22591,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>247.5606518777637</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>201.6485557026693</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -22636,13 +22636,13 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>115.6949632036871</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>519.3624388018133</v>
+        <v>119.3624388018133</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>58.21385845517733</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -22654,7 +22654,7 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>113.0916397727785</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -22703,22 +22703,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>61.55313599271381</v>
+        <v>461.5531359927138</v>
       </c>
       <c r="N4" t="n">
-        <v>113.5113539602095</v>
+        <v>453.8638987308433</v>
       </c>
       <c r="O4" t="n">
-        <v>587.1745476855723</v>
+        <v>187.1745476855723</v>
       </c>
       <c r="P4" t="n">
         <v>641.8653399512283</v>
       </c>
       <c r="Q4" t="n">
-        <v>489.694117545211</v>
+        <v>694.280266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>709.6559968336101</v>
+        <v>309.6559968336101</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22758,7 +22758,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>237.0695145734264</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -22770,7 +22770,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>117.6893104364534</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -22800,7 +22800,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>414.3082207672538</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -22815,7 +22815,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>127.6070577310094</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -22873,7 +22873,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>115.6949632036871</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -22910,16 +22910,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -22934,7 +22934,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>244.733560686389</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -22973,7 +22973,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -23007,7 +23007,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>117.6893104364534</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -23144,10 +23144,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>285.5362180555555</v>
@@ -23171,19 +23171,19 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>244.733560686389</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>367.51507078073</v>
+        <v>25.4654128746572</v>
       </c>
       <c r="M10" t="n">
-        <v>105.2670833627013</v>
+        <v>461.5531359927138</v>
       </c>
       <c r="N10" t="n">
         <v>513.5113539602095</v>
       </c>
       <c r="O10" t="n">
-        <v>187.1745476855723</v>
+        <v>587.1745476855723</v>
       </c>
       <c r="P10" t="n">
         <v>641.8653399512283</v>
@@ -23223,7 +23223,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>259.9993129555745</v>
       </c>
       <c r="C11" t="n">
         <v>227.4745782429939</v>
@@ -23238,10 +23238,10 @@
         <v>182.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>180.9171712819911</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>5.004856102449338</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23274,25 +23274,25 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>253.7020874003128</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>427.1540804682086</v>
       </c>
       <c r="V11" t="n">
-        <v>407.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>67.77470879492387</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>370.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>289.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -23302,7 +23302,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>162.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -23311,13 +23311,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>120.6720972219126</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>103.289988705216</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -23353,7 +23353,7 @@
         <v>297.3624388018133</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>90.19521177196367</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -23365,7 +23365,7 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>155.3939065521623</v>
+        <v>210.3731429098285</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -23381,13 +23381,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>65.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>63.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>58.98090483695654</v>
@@ -23408,7 +23408,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>22.73356068638896</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>145.51507078073</v>
@@ -23423,7 +23423,7 @@
         <v>365.1745476855723</v>
       </c>
       <c r="P13" t="n">
-        <v>108.3420470304175</v>
+        <v>419.8653399512283</v>
       </c>
       <c r="Q13" t="n">
         <v>472.280266425598</v>
@@ -23432,7 +23432,7 @@
         <v>487.6559968336101</v>
       </c>
       <c r="S13" t="n">
-        <v>133.8053977356423</v>
+        <v>64.57468217342448</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23447,10 +23447,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>25.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>65.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -23460,22 +23460,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>211.9993129555745</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>140.3391557398498</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>134.8896287080119</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>132.9171712819911</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -23511,22 +23511,22 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>205.7020874003128</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>312.9976018290664</v>
       </c>
       <c r="U14" t="n">
-        <v>379.1540804682087</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>359.8510241668239</v>
       </c>
       <c r="W14" t="n">
-        <v>368.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>112.128154668644</v>
+        <v>132.2149280036197</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -23648,25 +23648,25 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>97.51507078072996</v>
+        <v>97.51507078072999</v>
       </c>
       <c r="M16" t="n">
         <v>191.5531359927138</v>
       </c>
       <c r="N16" t="n">
-        <v>243.5113539602095</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>317.1745476855723</v>
+        <v>254.9394116597723</v>
       </c>
       <c r="P16" t="n">
-        <v>371.8653399512283</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>186.3244333219704</v>
+        <v>424.280266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>439.6559968336101</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -23706,16 +23706,16 @@
         <v>140.3391557398498</v>
       </c>
       <c r="E17" t="n">
-        <v>133.3786538343333</v>
+        <v>134.3632896068686</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>134.8896287080119</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>132.9171712819911</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>129.4049501608139</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23748,13 +23748,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>205.7020874003128</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>312.9976018290664</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>120.5033033060271</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -23885,7 +23885,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>97.51507078072996</v>
+        <v>97.51507078072999</v>
       </c>
       <c r="M19" t="n">
         <v>191.5531359927138</v>
@@ -23897,13 +23897,13 @@
         <v>317.1745476855723</v>
       </c>
       <c r="P19" t="n">
-        <v>32.7283787039463</v>
+        <v>371.8653399512283</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>439.6559968336101</v>
+        <v>100.5190355863281</v>
       </c>
       <c r="S19" t="n">
         <v>85.80539773564232</v>
@@ -23952,7 +23952,7 @@
         <v>132.9171712819911</v>
       </c>
       <c r="H20" t="n">
-        <v>129.4049501608139</v>
+        <v>129.4049501608138</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>205.7020874003128</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -24000,10 +24000,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>120.5033033060271</v>
       </c>
       <c r="Y20" t="n">
-        <v>156.1186485885207</v>
+        <v>241.3174326828064</v>
       </c>
     </row>
     <row r="21">
@@ -24092,13 +24092,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
         <v>2.725246648044674</v>
       </c>
       <c r="D22" t="n">
-        <v>15.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>10.98090483695654</v>
@@ -24122,13 +24122,13 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>86.33688074634554</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>136.4522519884422</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -24161,7 +24161,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>17.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -24171,10 +24171,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>211.9993129555745</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>179.4745782429939</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -24183,7 +24183,7 @@
         <v>134.3632896068686</v>
       </c>
       <c r="F23" t="n">
-        <v>134.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>132.9171712819911</v>
@@ -24228,16 +24228,16 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>165.4092827794802</v>
+        <v>379.1540804682087</v>
       </c>
       <c r="V23" t="n">
-        <v>359.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>368.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>257.8954399684865</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -24368,16 +24368,16 @@
         <v>243.5113539602095</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>317.1745476855723</v>
       </c>
       <c r="P25" t="n">
         <v>371.8653399512283</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>100.5190355863281</v>
       </c>
       <c r="R25" t="n">
-        <v>417.6935832719004</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>85.80539773564232</v>
@@ -24408,25 +24408,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>283.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>251.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>212.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>55.9862385409055</v>
+        <v>206.3632896068686</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>204.9171712819911</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>201.4049501608139</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24462,16 +24462,16 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>384.9976018290664</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>451.1540804682086</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>431.8510241668239</v>
+        <v>238.4053232618026</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>440.3734759809475</v>
       </c>
       <c r="X26" t="n">
         <v>394.2818334606677</v>
@@ -24490,19 +24490,19 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>163.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>149.9376868977026</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>144.6720972219126</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>141.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>127.289988705216</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -24538,13 +24538,13 @@
         <v>321.3624388018133</v>
       </c>
       <c r="S27" t="n">
-        <v>260.2138584551773</v>
+        <v>25.07264953383762</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>165.2948937958488</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -24566,7 +24566,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>89.11380033707866</v>
+        <v>50.51319102605252</v>
       </c>
       <c r="C28" t="n">
         <v>74.72524664804467</v>
@@ -24578,7 +24578,7 @@
         <v>82.98090483695654</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>76.38285596774193</v>
       </c>
       <c r="G28" t="n">
         <v>46.66698759562839</v>
@@ -24602,7 +24602,7 @@
         <v>263.5531359927138</v>
       </c>
       <c r="N28" t="n">
-        <v>195.488202881283</v>
+        <v>315.5113539602095</v>
       </c>
       <c r="O28" t="n">
         <v>389.1745476855723</v>
@@ -24617,7 +24617,7 @@
         <v>511.6559968336101</v>
       </c>
       <c r="S28" t="n">
-        <v>157.8053977356423</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24645,10 +24645,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>213.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>181.4745782429939</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -24660,10 +24660,10 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>134.9171712819911</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>131.4049501608138</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24702,10 +24702,10 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>381.1540804682087</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>361.8510241668239</v>
+        <v>158.8503006019487</v>
       </c>
       <c r="W29" t="n">
         <v>370.3734759809475</v>
@@ -24714,7 +24714,7 @@
         <v>324.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>77.64120860828947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -24724,7 +24724,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>90.69569070551825</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>90.69569070551839</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -24803,19 +24803,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>19.11380033707866</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>4.725246648044674</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>17.53621805555548</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>12.98090483695654</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>6.382855967741932</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -24833,13 +24833,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>99.51507078072996</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>193.5531359927138</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>245.5113539602095</v>
       </c>
       <c r="O31" t="n">
         <v>319.1745476855723</v>
@@ -24848,10 +24848,10 @@
         <v>373.8653399512283</v>
       </c>
       <c r="Q31" t="n">
-        <v>426.280266425598</v>
+        <v>211.9264333219704</v>
       </c>
       <c r="R31" t="n">
-        <v>404.4301063248653</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -24872,7 +24872,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>19.46535284946236</v>
       </c>
     </row>
     <row r="32">
@@ -24882,7 +24882,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>213.9993129555745</v>
       </c>
       <c r="C32" t="n">
         <v>181.4745782429939</v>
@@ -24891,16 +24891,16 @@
         <v>142.3391557398498</v>
       </c>
       <c r="E32" t="n">
-        <v>136.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>136.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>134.9171712819911</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>131.4049501608139</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -24936,7 +24936,7 @@
         <v>207.7020874003128</v>
       </c>
       <c r="T32" t="n">
-        <v>314.9976018290664</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -24945,13 +24945,13 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>370.3734759809475</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>324.2818334606677</v>
       </c>
       <c r="Y32" t="n">
-        <v>129.2131597150289</v>
+        <v>75.13117890459111</v>
       </c>
     </row>
     <row r="33">
@@ -24970,10 +24970,10 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>19.05944836764139</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>71.63624233787687</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -25009,7 +25009,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>90.69569070551833</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -25040,19 +25040,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>19.11380033707866</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>4.725246648044674</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>17.53621805555548</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>12.98090483695654</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>6.382855967741932</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -25070,7 +25070,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>99.51507078072999</v>
+        <v>99.51507078072996</v>
       </c>
       <c r="M34" t="n">
         <v>193.5531359927138</v>
@@ -25082,16 +25082,16 @@
         <v>319.1745476855723</v>
       </c>
       <c r="P34" t="n">
-        <v>373.8653399512283</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>292.13081201681</v>
+        <v>56.33037870394628</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>441.6559968336101</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>87.80539773564232</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25109,7 +25109,7 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>19.46535284946236</v>
       </c>
     </row>
     <row r="35">
@@ -25122,22 +25122,22 @@
         <v>213.9993129555745</v>
       </c>
       <c r="C35" t="n">
-        <v>164.1499320187521</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>142.3391557398498</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>136.3632896068686</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>134.9171712819911</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>131.4049501608138</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -25170,7 +25170,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>207.7020874003128</v>
+        <v>188.6784767963652</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -25179,7 +25179,7 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>361.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -25246,10 +25246,10 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>90.69569070551833</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>90.69569070551825</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
@@ -25277,7 +25277,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>19.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
         <v>4.725246648044674</v>
@@ -25322,7 +25322,7 @@
         <v>373.8653399512283</v>
       </c>
       <c r="Q37" t="n">
-        <v>211.9264333219704</v>
+        <v>250.5055865085114</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -25346,7 +25346,7 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>19.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -25407,19 +25407,19 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>207.7020874003128</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
         <v>314.9976018290664</v>
       </c>
       <c r="U38" t="n">
-        <v>173.4341636503532</v>
+        <v>10.76277506971837</v>
       </c>
       <c r="V38" t="n">
         <v>361.8510241668239</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>370.3734759809475</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -25450,10 +25450,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>30.86928276438013</v>
+        <v>30.86928276438016</v>
       </c>
       <c r="H39" t="n">
-        <v>59.82640794113811</v>
+        <v>59.82640794113809</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -25544,19 +25544,19 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>99.51507078072999</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>193.5531359927138</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>113.9388807463457</v>
       </c>
       <c r="P40" t="n">
-        <v>194.7360139241301</v>
+        <v>373.8653399512283</v>
       </c>
       <c r="Q40" t="n">
         <v>426.280266425598</v>
@@ -25611,7 +25611,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>281.4049501608138</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25644,13 +25644,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>357.7020874003128</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>464.9976018290664</v>
+        <v>163.8428116657706</v>
       </c>
       <c r="U41" t="n">
-        <v>92.01958574821703</v>
+        <v>76.15408046820528</v>
       </c>
       <c r="V41" t="n">
         <v>511.8510241668239</v>
@@ -25662,7 +25662,7 @@
         <v>474.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>393.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -25675,7 +25675,7 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>243.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -25684,16 +25684,16 @@
         <v>224.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>221.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>207.289988705216</v>
       </c>
       <c r="H42" t="n">
-        <v>209.8264079411381</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>52.51353902585579</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25720,28 +25720,28 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>381.8412036253658</v>
+        <v>401.3624388018133</v>
       </c>
       <c r="S42" t="n">
         <v>340.2138584551773</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>285.5457746514761</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>296.5106671915202</v>
       </c>
       <c r="W42" t="n">
         <v>314.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>301.8627394453875</v>
       </c>
       <c r="Y42" t="n">
-        <v>281.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -25793,7 +25793,7 @@
         <v>469.1745476855723</v>
       </c>
       <c r="P43" t="n">
-        <v>449.6029348764807</v>
+        <v>523.8653399512283</v>
       </c>
       <c r="Q43" t="n">
         <v>576.280266425598</v>
@@ -25814,7 +25814,7 @@
         <v>81.17031021621619</v>
       </c>
       <c r="W43" t="n">
-        <v>108.3728098387097</v>
+        <v>34.11040476396215</v>
       </c>
       <c r="X43" t="n">
         <v>129.4436454301076</v>
@@ -25830,7 +25830,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>481.9993129555745</v>
+        <v>341.4298959992302</v>
       </c>
       <c r="C44" t="n">
         <v>449.4745782429939</v>
@@ -25848,7 +25848,7 @@
         <v>402.9171712819911</v>
       </c>
       <c r="H44" t="n">
-        <v>399.4049501608138</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25878,25 +25878,25 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>198.1003224463849</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>475.7020874003128</v>
+        <v>20.70208740031126</v>
       </c>
       <c r="T44" t="n">
-        <v>582.9976018290664</v>
+        <v>127.9976018290647</v>
       </c>
       <c r="U44" t="n">
-        <v>194.1540804681927</v>
+        <v>649.1540804682087</v>
       </c>
       <c r="V44" t="n">
-        <v>346.7763346033237</v>
+        <v>629.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>183.3734759809322</v>
+        <v>638.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>137.2818334606527</v>
+        <v>592.2818334606677</v>
       </c>
       <c r="Y44" t="n">
         <v>511.3174326828064</v>
@@ -25909,28 +25909,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>384.5565566463266</v>
+        <v>61.59220141776979</v>
       </c>
       <c r="C45" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>325.289988705216</v>
       </c>
       <c r="H45" t="n">
         <v>327.8264079411381</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>201.6485557026693</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25954,13 +25954,13 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>115.6949632036871</v>
       </c>
       <c r="R45" t="n">
-        <v>283.6050893232315</v>
+        <v>519.3624388018133</v>
       </c>
       <c r="S45" t="n">
-        <v>3.213858455160107</v>
+        <v>458.2138584551773</v>
       </c>
       <c r="T45" t="n">
         <v>403.5457746514761</v>
@@ -25972,13 +25972,13 @@
         <v>414.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X45" t="n">
         <v>419.8627394453875</v>
       </c>
       <c r="Y45" t="n">
-        <v>399.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1056799.725812281</v>
+        <v>1056799.72581228</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1976983.336229654</v>
+        <v>1976983.336229653</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2897166.946647027</v>
+        <v>2897166.946647026</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3720132.229451677</v>
+        <v>3720132.229451678</v>
       </c>
     </row>
     <row r="6">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6468647.563256567</v>
+        <v>6468647.56325657</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7384812.422589566</v>
+        <v>7384812.422589567</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8154458.778686065</v>
+        <v>8154458.778686066</v>
       </c>
     </row>
     <row r="11">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9966881.042827591</v>
+        <v>9966881.042827589</v>
       </c>
     </row>
     <row r="13">
@@ -26278,7 +26278,7 @@
         <v>1031721.017740692</v>
       </c>
       <c r="E2" t="n">
-        <v>924155.0939629725</v>
+        <v>924155.0939629728</v>
       </c>
       <c r="F2" t="n">
         <v>1027215.145312761</v>
@@ -26293,7 +26293,7 @@
         <v>1027215.145312761</v>
       </c>
       <c r="J2" t="n">
-        <v>865399.2541645929</v>
+        <v>865399.2541645933</v>
       </c>
       <c r="K2" t="n">
         <v>1015967.76305929</v>
@@ -26308,10 +26308,10 @@
         <v>1015967.76305929</v>
       </c>
       <c r="O2" t="n">
-        <v>684288.2341203467</v>
+        <v>684288.2341203461</v>
       </c>
       <c r="P2" t="n">
-        <v>403890.6742355747</v>
+        <v>403890.6742355746</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>522443.9175261983</v>
+        <v>519431.9533593054</v>
       </c>
       <c r="C4" t="n">
-        <v>520895.8177336115</v>
+        <v>517883.8535667188</v>
       </c>
       <c r="D4" t="n">
-        <v>519345.6178470306</v>
+        <v>516333.6536801378</v>
       </c>
       <c r="E4" t="n">
-        <v>450618.642382932</v>
+        <v>447634.9236756904</v>
       </c>
       <c r="F4" t="n">
-        <v>512285.8454909147</v>
+        <v>509301.669182142</v>
       </c>
       <c r="G4" t="n">
-        <v>510739.5336602722</v>
+        <v>507755.3573514995</v>
       </c>
       <c r="H4" t="n">
-        <v>509191.0756370474</v>
+        <v>506206.8993282748</v>
       </c>
       <c r="I4" t="n">
-        <v>507640.4559412895</v>
+        <v>504656.2796325169</v>
       </c>
       <c r="J4" t="n">
-        <v>409492.9642084554</v>
+        <v>406557.2078227153</v>
       </c>
       <c r="K4" t="n">
-        <v>498537.5811624979</v>
+        <v>495598.3977257177</v>
       </c>
       <c r="L4" t="n">
-        <v>496997.1402473961</v>
+        <v>494057.9568106153</v>
       </c>
       <c r="M4" t="n">
-        <v>495454.497624781</v>
+        <v>492515.3141880009</v>
       </c>
       <c r="N4" t="n">
-        <v>493909.6369385927</v>
+        <v>490970.4535018137</v>
       </c>
       <c r="O4" t="n">
-        <v>297351.637654884</v>
+        <v>294415.8812691434</v>
       </c>
       <c r="P4" t="n">
-        <v>132775.7988702889</v>
+        <v>129840.0424845487</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>72889.50021449411</v>
+        <v>75901.46438138674</v>
       </c>
       <c r="C6" t="n">
-        <v>444004.6000070808</v>
+        <v>447016.5641739734</v>
       </c>
       <c r="D6" t="n">
-        <v>445554.7998936617</v>
+        <v>448566.7640605546</v>
       </c>
       <c r="E6" t="n">
-        <v>244080.1335800405</v>
+        <v>247063.8522872823</v>
       </c>
       <c r="F6" t="n">
-        <v>420637.6698218463</v>
+        <v>423621.8461306189</v>
       </c>
       <c r="G6" t="n">
-        <v>460583.9816524884</v>
+        <v>463568.1579612615</v>
       </c>
       <c r="H6" t="n">
-        <v>462132.4396757134</v>
+        <v>465116.6159844861</v>
       </c>
       <c r="I6" t="n">
-        <v>463683.0593714713</v>
+        <v>466667.2356802439</v>
       </c>
       <c r="J6" t="n">
-        <v>126880.4279561375</v>
+        <v>129816.184341878</v>
       </c>
       <c r="K6" t="n">
-        <v>368279.4898967922</v>
+        <v>371218.6733335723</v>
       </c>
       <c r="L6" t="n">
-        <v>464219.9308118943</v>
+        <v>467159.1142486745</v>
       </c>
       <c r="M6" t="n">
-        <v>465762.5734345088</v>
+        <v>468701.7568712892</v>
       </c>
       <c r="N6" t="n">
-        <v>467307.4341206976</v>
+        <v>470246.6175574763</v>
       </c>
       <c r="O6" t="n">
-        <v>344796.2544654627</v>
+        <v>347732.0108512027</v>
       </c>
       <c r="P6" t="n">
-        <v>238894.6753652858</v>
+        <v>241830.4317510258</v>
       </c>
     </row>
   </sheetData>
@@ -26987,13 +26987,13 @@
         <v>48</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>150</v>
@@ -27002,7 +27002,7 @@
         <v>118</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -27454,7 +27454,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>117.6893104364534</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>198.1003224463849</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27512,13 +27512,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -27527,13 +27527,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.289988705216</v>
       </c>
       <c r="H3" t="n">
-        <v>327.8264079411381</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>201.6485557026693</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,13 +27557,13 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>115.6949632036871</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T3" t="n">
         <v>400</v>
@@ -27575,10 +27575,10 @@
         <v>400</v>
       </c>
       <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
         <v>400</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>399.3913927661343</v>
@@ -27624,22 +27624,22 @@
         <v>367.51507078073</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>59.64745522936619</v>
+      </c>
+      <c r="O4" t="n">
         <v>400</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
         <v>400</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>204.586148880387</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>355.8053977356423</v>
@@ -27679,7 +27679,7 @@
         <v>400</v>
       </c>
       <c r="E5" t="n">
-        <v>167.2937750334422</v>
+        <v>400</v>
       </c>
       <c r="F5" t="n">
         <v>400</v>
@@ -27688,7 +27688,7 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>399.4049501608138</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27721,13 +27721,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>400</v>
+        <v>61.393866633059</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
       </c>
       <c r="U5" t="n">
-        <v>317.2302158000929</v>
+        <v>400</v>
       </c>
       <c r="V5" t="n">
         <v>400</v>
@@ -27749,7 +27749,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>361.0999124455193</v>
@@ -27797,7 +27797,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>400</v>
+        <v>65.08974617516787</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
@@ -27806,16 +27806,16 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>196.2281527325287</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27831,16 +27831,16 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
         <v>244.6669875956284</v>
@@ -27855,7 +27855,7 @@
         <v>8.623161950661881</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>244.733560686389</v>
       </c>
       <c r="L7" t="n">
         <v>367.51507078073</v>
@@ -27894,7 +27894,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
         <v>287.4653528494624</v>
@@ -27919,10 +27919,10 @@
         <v>400</v>
       </c>
       <c r="F8" t="n">
+        <v>5.803872524123562</v>
+      </c>
+      <c r="G8" t="n">
         <v>400</v>
-      </c>
-      <c r="G8" t="n">
-        <v>356.1197069796295</v>
       </c>
       <c r="H8" t="n">
         <v>399.4049501608138</v>
@@ -27970,7 +27970,7 @@
         <v>400</v>
       </c>
       <c r="W8" t="n">
-        <v>167.3734759809475</v>
+        <v>400</v>
       </c>
       <c r="X8" t="n">
         <v>400</v>
@@ -27986,10 +27986,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -28004,10 +28004,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>327.8264079411381</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>201.6485557026693</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,16 +28031,16 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>115.6949632036871</v>
       </c>
       <c r="R9" t="n">
-        <v>198.9307919792545</v>
+        <v>400</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>400</v>
+        <v>299.417334223606</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28065,10 +28065,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -28092,19 +28092,19 @@
         <v>8.623161950661881</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>244.733560686389</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>342.0496579060728</v>
       </c>
       <c r="M10" t="n">
-        <v>356.2860526300125</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -28244,7 +28244,7 @@
         <v>222</v>
       </c>
       <c r="I12" t="n">
-        <v>222</v>
+        <v>201.6485557026693</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28259,7 +28259,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>61.5657420519843</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -28268,7 +28268,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>156.9092609583407</v>
+        <v>115.6949632036871</v>
       </c>
       <c r="R12" t="n">
         <v>222</v>
@@ -28481,7 +28481,7 @@
         <v>270</v>
       </c>
       <c r="I15" t="n">
-        <v>261.7888214823528</v>
+        <v>201.6485557026693</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28496,7 +28496,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>60.1402657796834</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -28718,7 +28718,7 @@
         <v>270</v>
       </c>
       <c r="I18" t="n">
-        <v>201.6485557026693</v>
+        <v>261.7888214823528</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28742,7 +28742,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>175.8352289833706</v>
+        <v>115.6949632036871</v>
       </c>
       <c r="R18" t="n">
         <v>270</v>
@@ -29453,7 +29453,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>115.6949632036697</v>
+        <v>115.6949632036871</v>
       </c>
       <c r="R27" t="n">
         <v>198</v>
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>115.6949632036701</v>
+        <v>115.6949632036871</v>
       </c>
       <c r="R30" t="n">
         <v>268</v>
@@ -30164,7 +30164,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>115.6949632036701</v>
+        <v>115.6949632036871</v>
       </c>
       <c r="R36" t="n">
         <v>268</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>198.1003224463691</v>
+        <v>198.1003224463849</v>
       </c>
       <c r="S38" t="n">
         <v>268</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>115.6949632036713</v>
+        <v>115.6949632036871</v>
       </c>
       <c r="R39" t="n">
         <v>268</v>
@@ -30638,7 +30638,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>115.6949632037056</v>
+        <v>115.6949632036871</v>
       </c>
       <c r="R42" t="n">
         <v>118</v>
@@ -34749,7 +34749,7 @@
         <v>471</v>
       </c>
       <c r="L2" t="n">
-        <v>471</v>
+        <v>471.0000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>471</v>
@@ -34983,10 +34983,10 @@
         <v>471</v>
       </c>
       <c r="K5" t="n">
-        <v>471.0000000000001</v>
+        <v>471</v>
       </c>
       <c r="L5" t="n">
-        <v>470.9999999999999</v>
+        <v>471</v>
       </c>
       <c r="M5" t="n">
         <v>471</v>
@@ -35457,16 +35457,16 @@
         <v>466.5727403913177</v>
       </c>
       <c r="K11" t="n">
-        <v>470.9999999999999</v>
+        <v>106.8767185929648</v>
       </c>
       <c r="L11" t="n">
+        <v>132.5900201005026</v>
+      </c>
+      <c r="M11" t="n">
         <v>471</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
       <c r="N11" t="n">
-        <v>264.5455143338568</v>
+        <v>471</v>
       </c>
       <c r="O11" t="n">
         <v>71.3165475113347</v>
@@ -35475,7 +35475,7 @@
         <v>120.5348947331879</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>25.07877564038944</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35530,7 +35530,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>20.35144429733072</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>167.6809552942795</v>
@@ -35545,7 +35545,7 @@
         <v>200.8550421645043</v>
       </c>
       <c r="N12" t="n">
-        <v>251.5462765237492</v>
+        <v>313.1120185757334</v>
       </c>
       <c r="O12" t="n">
         <v>348.4157294499162</v>
@@ -35554,7 +35554,7 @@
         <v>199.5097969674834</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.21429775465357</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35694,16 +35694,16 @@
         <v>466.5727403913177</v>
       </c>
       <c r="K14" t="n">
-        <v>106.8767185929648</v>
+        <v>471</v>
       </c>
       <c r="L14" t="n">
-        <v>162.8072685454379</v>
+        <v>132.5900201005026</v>
       </c>
       <c r="M14" t="n">
         <v>471</v>
       </c>
       <c r="N14" t="n">
-        <v>471</v>
+        <v>162.7862752199467</v>
       </c>
       <c r="O14" t="n">
         <v>71.3165475113347</v>
@@ -35712,7 +35712,7 @@
         <v>120.5348947331879</v>
       </c>
       <c r="Q14" t="n">
-        <v>25.69230818202226</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35767,7 +35767,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>60.14026577968347</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>167.6809552942795</v>
@@ -35782,7 +35782,7 @@
         <v>200.8550421645043</v>
       </c>
       <c r="N15" t="n">
-        <v>251.5462765237492</v>
+        <v>311.6865423034325</v>
       </c>
       <c r="O15" t="n">
         <v>348.4157294499162</v>
@@ -35840,10 +35840,10 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>25.3330124043716</v>
+        <v>25.33301240437161</v>
       </c>
       <c r="H16" t="n">
-        <v>44.57972635739779</v>
+        <v>44.57972635739777</v>
       </c>
       <c r="I16" t="n">
         <v>104.7005115929965</v>
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>66.48525225008437</v>
+        <v>466.5727403913177</v>
       </c>
       <c r="K17" t="n">
+        <v>106.8767185929648</v>
+      </c>
+      <c r="L17" t="n">
+        <v>162.8072685454042</v>
+      </c>
+      <c r="M17" t="n">
         <v>471</v>
       </c>
-      <c r="L17" t="n">
-        <v>132.5900201005026</v>
-      </c>
-      <c r="M17" t="n">
-        <v>91.87376336114232</v>
-      </c>
       <c r="N17" t="n">
-        <v>471.0000000000011</v>
+        <v>25.69230818202141</v>
       </c>
       <c r="O17" t="n">
         <v>71.3165475113347</v>
@@ -36004,7 +36004,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>60.14026577968347</v>
       </c>
       <c r="J18" t="n">
         <v>167.6809552942795</v>
@@ -36028,7 +36028,7 @@
         <v>199.5097969674834</v>
       </c>
       <c r="Q18" t="n">
-        <v>60.14026577968344</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36077,10 +36077,10 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>25.3330124043716</v>
+        <v>25.33301240437161</v>
       </c>
       <c r="H19" t="n">
-        <v>44.57972635739779</v>
+        <v>44.57972635739777</v>
       </c>
       <c r="I19" t="n">
         <v>104.7005115929965</v>
@@ -36165,19 +36165,19 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>36.26800380516094</v>
+        <v>466.5727403913177</v>
       </c>
       <c r="K20" t="n">
-        <v>471.0000000000001</v>
+        <v>162.7862752199084</v>
       </c>
       <c r="L20" t="n">
         <v>132.5900201005026</v>
       </c>
       <c r="M20" t="n">
-        <v>471.0000000000017</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>471.0000000000017</v>
+        <v>471</v>
       </c>
       <c r="O20" t="n">
         <v>71.3165475113347</v>
@@ -36186,7 +36186,7 @@
         <v>120.5348947331879</v>
       </c>
       <c r="Q20" t="n">
-        <v>122.0910118060742</v>
+        <v>471</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36314,10 +36314,10 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>25.33301240437161</v>
+        <v>25.3330124043716</v>
       </c>
       <c r="H22" t="n">
-        <v>44.57972635739777</v>
+        <v>44.57972635739779</v>
       </c>
       <c r="I22" t="n">
         <v>104.7005115929965</v>
@@ -36405,16 +36405,16 @@
         <v>36.26800380516094</v>
       </c>
       <c r="K23" t="n">
-        <v>471.0000000000001</v>
+        <v>137.0939670379057</v>
       </c>
       <c r="L23" t="n">
-        <v>132.5900201005026</v>
+        <v>471</v>
       </c>
       <c r="M23" t="n">
-        <v>471.0000000000024</v>
+        <v>117.5870648686816</v>
       </c>
       <c r="N23" t="n">
-        <v>122.0910118060985</v>
+        <v>471</v>
       </c>
       <c r="O23" t="n">
         <v>71.3165475113347</v>
@@ -36423,7 +36423,7 @@
         <v>120.5348947331879</v>
       </c>
       <c r="Q23" t="n">
-        <v>471.0000000000024</v>
+        <v>471</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36639,7 +36639,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>455</v>
+        <v>36.26800380516094</v>
       </c>
       <c r="K26" t="n">
         <v>106.8767185929648</v>
@@ -36648,10 +36648,10 @@
         <v>132.5900201005026</v>
       </c>
       <c r="M26" t="n">
+        <v>424.0299768730106</v>
+      </c>
+      <c r="N26" t="n">
         <v>455</v>
-      </c>
-      <c r="N26" t="n">
-        <v>5.297980678171665</v>
       </c>
       <c r="O26" t="n">
         <v>71.3165475113347</v>
@@ -36721,7 +36721,7 @@
         <v>167.6809552942795</v>
       </c>
       <c r="K27" t="n">
-        <v>261.9080707732201</v>
+        <v>261.9080707732027</v>
       </c>
       <c r="L27" t="n">
         <v>371.7002904430266</v>
@@ -36739,7 +36739,7 @@
         <v>199.5097969674834</v>
       </c>
       <c r="Q27" t="n">
-        <v>-1.745494882190469e-11</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36876,19 +36876,19 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>455.000000000004</v>
+        <v>455</v>
       </c>
       <c r="K29" t="n">
-        <v>333.1785241864548</v>
+        <v>333.1785241871938</v>
       </c>
       <c r="L29" t="n">
         <v>132.5900201005026</v>
       </c>
       <c r="M29" t="n">
-        <v>455.000000000004</v>
+        <v>455</v>
       </c>
       <c r="N29" t="n">
-        <v>9.892823991403873</v>
+        <v>9.892823991430816</v>
       </c>
       <c r="O29" t="n">
         <v>71.3165475113347</v>
@@ -36897,7 +36897,7 @@
         <v>120.5348947331879</v>
       </c>
       <c r="Q29" t="n">
-        <v>455.000000000004</v>
+        <v>455</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36967,16 +36967,16 @@
         <v>200.8550421645043</v>
       </c>
       <c r="N30" t="n">
-        <v>249.7584832222151</v>
+        <v>251.5462765237492</v>
       </c>
       <c r="O30" t="n">
-        <v>348.4157294499162</v>
+        <v>346.6279361483651</v>
       </c>
       <c r="P30" t="n">
         <v>199.5097969674834</v>
       </c>
       <c r="Q30" t="n">
-        <v>-1.565437299629759e-12</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37113,19 +37113,19 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>455.000000000004</v>
+        <v>36.26800380516094</v>
       </c>
       <c r="K32" t="n">
-        <v>455.0000000000001</v>
+        <v>106.8767185929648</v>
       </c>
       <c r="L32" t="n">
+        <v>358.8918256947231</v>
+      </c>
+      <c r="M32" t="n">
+        <v>428.6248201862696</v>
+      </c>
+      <c r="N32" t="n">
         <v>455</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>20.6613682791459</v>
       </c>
       <c r="O32" t="n">
         <v>71.3165475113347</v>
@@ -37134,7 +37134,7 @@
         <v>120.5348947331879</v>
       </c>
       <c r="Q32" t="n">
-        <v>455.000000000004</v>
+        <v>455</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37204,10 +37204,10 @@
         <v>200.8550421645043</v>
       </c>
       <c r="N33" t="n">
-        <v>249.7584832221981</v>
+        <v>251.5462765237492</v>
       </c>
       <c r="O33" t="n">
-        <v>348.4157294499162</v>
+        <v>346.6279361483651</v>
       </c>
       <c r="P33" t="n">
         <v>199.5097969674834</v>
@@ -37262,10 +37262,10 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>23.33301240437161</v>
+        <v>23.3330124043716</v>
       </c>
       <c r="H34" t="n">
-        <v>42.57972635739777</v>
+        <v>42.57972635739779</v>
       </c>
       <c r="I34" t="n">
         <v>102.7005115929965</v>
@@ -37350,19 +37350,19 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>36.26800380516094</v>
+        <v>455</v>
       </c>
       <c r="K35" t="n">
+        <v>106.8767185929648</v>
+      </c>
+      <c r="L35" t="n">
+        <v>358.8918256947316</v>
+      </c>
+      <c r="M35" t="n">
         <v>455</v>
       </c>
-      <c r="L35" t="n">
-        <v>455</v>
-      </c>
-      <c r="M35" t="n">
-        <v>391.5394996812801</v>
-      </c>
       <c r="N35" t="n">
-        <v>455.000000000004</v>
+        <v>9.892823991430816</v>
       </c>
       <c r="O35" t="n">
         <v>71.3165475113347</v>
@@ -37371,7 +37371,7 @@
         <v>120.5348947331879</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>455</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37441,16 +37441,16 @@
         <v>200.8550421645043</v>
       </c>
       <c r="N36" t="n">
-        <v>339.5973425957879</v>
+        <v>251.5462765237492</v>
       </c>
       <c r="O36" t="n">
-        <v>348.4157294499162</v>
+        <v>346.6279361483651</v>
       </c>
       <c r="P36" t="n">
         <v>199.5097969674834</v>
       </c>
       <c r="Q36" t="n">
-        <v>-1.699560806343351e-11</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37587,19 +37587,19 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>36.26800380516094</v>
+        <v>455</v>
       </c>
       <c r="K38" t="n">
-        <v>333.1785241852243</v>
+        <v>106.8767185929648</v>
       </c>
       <c r="L38" t="n">
-        <v>132.5900201005025</v>
+        <v>358.8918256947204</v>
       </c>
       <c r="M38" t="n">
-        <v>428.6248201862379</v>
+        <v>455</v>
       </c>
       <c r="N38" t="n">
-        <v>455.000000000004</v>
+        <v>9.892823991430475</v>
       </c>
       <c r="O38" t="n">
         <v>71.3165475113347</v>
@@ -37608,10 +37608,10 @@
         <v>120.5348947331879</v>
       </c>
       <c r="Q38" t="n">
-        <v>455.000000000004</v>
+        <v>455</v>
       </c>
       <c r="R38" t="n">
-        <v>-9.209255684715188e-12</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -37669,7 +37669,7 @@
         <v>167.6809552942795</v>
       </c>
       <c r="K39" t="n">
-        <v>261.9080707732182</v>
+        <v>261.9080707732027</v>
       </c>
       <c r="L39" t="n">
         <v>371.7002904430266</v>
@@ -37687,7 +37687,7 @@
         <v>199.5097969674834</v>
       </c>
       <c r="Q39" t="n">
-        <v>-1.584725616725557e-11</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37736,10 +37736,10 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>23.33301240437161</v>
+        <v>23.3330124043716</v>
       </c>
       <c r="H40" t="n">
-        <v>42.57972635739777</v>
+        <v>42.57972635739779</v>
       </c>
       <c r="I40" t="n">
         <v>102.7005115929965</v>
@@ -37824,19 +37824,19 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>455.000000000004</v>
+        <v>455</v>
       </c>
       <c r="K41" t="n">
-        <v>106.8767185929649</v>
+        <v>106.8767185929648</v>
       </c>
       <c r="L41" t="n">
         <v>132.5900201005026</v>
       </c>
       <c r="M41" t="n">
-        <v>5.297980678159837</v>
+        <v>455</v>
       </c>
       <c r="N41" t="n">
-        <v>455.000000000004</v>
+        <v>455</v>
       </c>
       <c r="O41" t="n">
         <v>71.3165475113347</v>
@@ -37845,7 +37845,7 @@
         <v>120.5348947331879</v>
       </c>
       <c r="Q41" t="n">
-        <v>455.000000000004</v>
+        <v>5.297980678171665</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37909,7 +37909,7 @@
         <v>263.6958640747536</v>
       </c>
       <c r="L42" t="n">
-        <v>369.9124971414757</v>
+        <v>371.7002904430266</v>
       </c>
       <c r="M42" t="n">
         <v>200.8550421645043</v>
@@ -37918,7 +37918,7 @@
         <v>251.5462765237492</v>
       </c>
       <c r="O42" t="n">
-        <v>348.4157294499162</v>
+        <v>346.6279361483651</v>
       </c>
       <c r="P42" t="n">
         <v>199.5097969674834</v>
@@ -38061,19 +38061,19 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>455</v>
+        <v>36.26800380516094</v>
       </c>
       <c r="K44" t="n">
-        <v>455</v>
+        <v>106.8767185929648</v>
       </c>
       <c r="L44" t="n">
         <v>132.5900201005026</v>
       </c>
       <c r="M44" t="n">
+        <v>424.0299768730106</v>
+      </c>
+      <c r="N44" t="n">
         <v>455</v>
-      </c>
-      <c r="N44" t="n">
-        <v>112.1746992711363</v>
       </c>
       <c r="O44" t="n">
         <v>71.3165475113347</v>
@@ -38082,7 +38082,7 @@
         <v>120.5348947331879</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>455</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38143,10 +38143,10 @@
         <v>167.6809552942795</v>
       </c>
       <c r="K45" t="n">
-        <v>261.9080707732027</v>
+        <v>263.6958640747536</v>
       </c>
       <c r="L45" t="n">
-        <v>371.7002904430266</v>
+        <v>369.9124971414757</v>
       </c>
       <c r="M45" t="n">
         <v>200.8550421645043</v>
